--- a/data/Vales.xlsx
+++ b/data/Vales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C495E90-D9E1-459D-8C8C-10E08C2C1BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B60E4C34-707D-42B3-8623-DDC0ABD8C3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{E17B0997-73A2-49BF-8FD7-6792AA05DE7F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4418" uniqueCount="1234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5261" uniqueCount="1431">
   <si>
     <t>MATRICULA</t>
   </si>
@@ -3738,6 +3738,597 @@
   </si>
   <si>
     <t>575,04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABNER VICTOR DE LARA BRELAZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADONIRAN MORAES DA SILVA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDERMESSON JORGE DOS SANTOS </t>
+  </si>
+  <si>
+    <t>ALESSANDRO ALVES NOVAES</t>
+  </si>
+  <si>
+    <t>ALEXANDRE BARBOSA</t>
+  </si>
+  <si>
+    <t>ANDERSON DE ALBUQUERQUE CAVALCANTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDERSON LUIS DO NASCIMENTO DA SILVA </t>
+  </si>
+  <si>
+    <t>ANDRE LUIZ PEREIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIO MARCOS DE JESUS </t>
+  </si>
+  <si>
+    <t>BRUNO CARDOSO DOS SANTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS EDUARDO VIDAL SILVA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS RAFAEL CARNEIRO DOS REIS </t>
+  </si>
+  <si>
+    <t>CLAUDECI FRANCISCO DE SOUSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLEITON MENDES MUNIZ </t>
+  </si>
+  <si>
+    <t>CRISTIAN ALISSON VIEIRA MESQUITA</t>
+  </si>
+  <si>
+    <t>CRISTIANO FIGUEIRO DA SILVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTIANO PAIVA DOS SANTOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARLAN ALESSANDRO LAURENTINO </t>
+  </si>
+  <si>
+    <t>DIOGO FERREIRA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>EDSON  VARELA DA SILVA</t>
+  </si>
+  <si>
+    <t>EDUARDO DA ROCHA</t>
+  </si>
+  <si>
+    <t>ERNANDO DO CARMO LIMA</t>
+  </si>
+  <si>
+    <t>FABIO JOSE GOEBEL</t>
+  </si>
+  <si>
+    <t>FELIPE HALLAI</t>
+  </si>
+  <si>
+    <t>FRANCISCO FORGANES DOS SANTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANECIR OLIVEIRA DA SILVA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABRIEL FELIPE FLORES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEOVANI SOARES DIAS FERMINIANO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUILHERME ALVES MORAIS </t>
+  </si>
+  <si>
+    <t>ISRAEL NOGUEIRA MARTINS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JADSON FERNANDO DE ANDRADE </t>
+  </si>
+  <si>
+    <t>JEAN FERNANDES TEIXEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEAN VITOR FERNANDES MARTENS </t>
+  </si>
+  <si>
+    <t>JEFFERSON DOS SANTOS SILVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO GABRIEL DA PAIXÃO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO VICTOR DE JESUS CORREA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO VITOR APARECIDO DA SILVA DE ASSIS </t>
+  </si>
+  <si>
+    <t>JONNAS SANTOS SILVA</t>
+  </si>
+  <si>
+    <t>JOSAFA FERREIRA RODRIGUES</t>
+  </si>
+  <si>
+    <t>JOSE ARNALDO DOS SANTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSENILDO GOMES DE OLIVEIRA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE NILSON ROSA DA SILVA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSIVAM CARDOSO DA SILVA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIANO CASTEDO MENDES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUNIOR BARBOSA SANTOS DOS ANJOS </t>
+  </si>
+  <si>
+    <t>LEANDRO DUARTE DA SILVA AGUIAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEONARDO FERNANDE DE SOUSA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEONARDO SERGIO SANTANA DA SILVA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCAS HENRIQUE FARIAS DA SILVA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCAS PEDRO DE JESUS SILVA </t>
+  </si>
+  <si>
+    <t>LUIZ FELIPE RODRIGUES DOS SANTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ HENRIQUE CAMARGO </t>
+  </si>
+  <si>
+    <t>LUIZ ROBERTO RAIMUNDO RIBEIRO</t>
+  </si>
+  <si>
+    <t>MARCELLO COELHO FELIX</t>
+  </si>
+  <si>
+    <t>MARCELO ALMEIDA DE MELLO RIBEIRO</t>
+  </si>
+  <si>
+    <t>MARCELO ODAIR SANTOS DA SILVA</t>
+  </si>
+  <si>
+    <t>MARCIO VINICIUS MOREIRA GOMES DE SOUZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS DANIEL SANTOS DE MATOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS ROBERTO DOS SANTOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATHEUS DA CONCEIÇÃO MOURA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATHEUS PIO DE OLIVEIRA </t>
+  </si>
+  <si>
+    <t>MAURO LUCIO PEREIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RICARDO CASTILHO IGLESIAS </t>
+  </si>
+  <si>
+    <t>ROBSON DA CRUZ FREITAS</t>
+  </si>
+  <si>
+    <t>RODRIGO ROVARIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROGERIO BISPO DOS SANTOS </t>
+  </si>
+  <si>
+    <t>ROGERIO DE SOUZA</t>
+  </si>
+  <si>
+    <t>WAGNER DE LIMA RIBEIRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WEVERTON ORIALBA NOGUEIRA </t>
+  </si>
+  <si>
+    <t>WILLIAN BEZERRA DA SILVA</t>
+  </si>
+  <si>
+    <t>539,04</t>
+  </si>
+  <si>
+    <t>120,74</t>
+  </si>
+  <si>
+    <t>38,64</t>
+  </si>
+  <si>
+    <t>287,62</t>
+  </si>
+  <si>
+    <t>268,92</t>
+  </si>
+  <si>
+    <t>4,02</t>
+  </si>
+  <si>
+    <t>708,25</t>
+  </si>
+  <si>
+    <t>2,70</t>
+  </si>
+  <si>
+    <t>119,00</t>
+  </si>
+  <si>
+    <t>300,30</t>
+  </si>
+  <si>
+    <t>186,86</t>
+  </si>
+  <si>
+    <t>155,00</t>
+  </si>
+  <si>
+    <t>129,34</t>
+  </si>
+  <si>
+    <t>116,63</t>
+  </si>
+  <si>
+    <t>137,60</t>
+  </si>
+  <si>
+    <t>264,94</t>
+  </si>
+  <si>
+    <t>76,00</t>
+  </si>
+  <si>
+    <t>76,22</t>
+  </si>
+  <si>
+    <t>164,34</t>
+  </si>
+  <si>
+    <t>84,92</t>
+  </si>
+  <si>
+    <t>228,15</t>
+  </si>
+  <si>
+    <t>4,05</t>
+  </si>
+  <si>
+    <t>250,28</t>
+  </si>
+  <si>
+    <t>303,75</t>
+  </si>
+  <si>
+    <t>47,10</t>
+  </si>
+  <si>
+    <t>92,65</t>
+  </si>
+  <si>
+    <t>13,35</t>
+  </si>
+  <si>
+    <t>573,47</t>
+  </si>
+  <si>
+    <t>407,53</t>
+  </si>
+  <si>
+    <t>31,92</t>
+  </si>
+  <si>
+    <t>94,57</t>
+  </si>
+  <si>
+    <t>68,39</t>
+  </si>
+  <si>
+    <t>30,40</t>
+  </si>
+  <si>
+    <t>52,20</t>
+  </si>
+  <si>
+    <t>1,34</t>
+  </si>
+  <si>
+    <t>128,64</t>
+  </si>
+  <si>
+    <t>144,72</t>
+  </si>
+  <si>
+    <t>294,50</t>
+  </si>
+  <si>
+    <t>19,32</t>
+  </si>
+  <si>
+    <t>384,62</t>
+  </si>
+  <si>
+    <t>38,42</t>
+  </si>
+  <si>
+    <t>134,36</t>
+  </si>
+  <si>
+    <t>338,00</t>
+  </si>
+  <si>
+    <t>472,26</t>
+  </si>
+  <si>
+    <t>111,52</t>
+  </si>
+  <si>
+    <t>338,33</t>
+  </si>
+  <si>
+    <t>28,45</t>
+  </si>
+  <si>
+    <t>29,76</t>
+  </si>
+  <si>
+    <t>146,10</t>
+  </si>
+  <si>
+    <t>269,87</t>
+  </si>
+  <si>
+    <t>104,40</t>
+  </si>
+  <si>
+    <t>1,35</t>
+  </si>
+  <si>
+    <t>60,00</t>
+  </si>
+  <si>
+    <t>286,97</t>
+  </si>
+  <si>
+    <t>105,80</t>
+  </si>
+  <si>
+    <t>18,24</t>
+  </si>
+  <si>
+    <t>12,12</t>
+  </si>
+  <si>
+    <t>203,32</t>
+  </si>
+  <si>
+    <t>63,84</t>
+  </si>
+  <si>
+    <t>247,92</t>
+  </si>
+  <si>
+    <t>266,66</t>
+  </si>
+  <si>
+    <t>139,33</t>
+  </si>
+  <si>
+    <t>129,62</t>
+  </si>
+  <si>
+    <t>146,46</t>
+  </si>
+  <si>
+    <t>57,39</t>
+  </si>
+  <si>
+    <t>48,36</t>
+  </si>
+  <si>
+    <t>333,26</t>
+  </si>
+  <si>
+    <t>486,30</t>
+  </si>
+  <si>
+    <t>29,29</t>
+  </si>
+  <si>
+    <t>122,40</t>
+  </si>
+  <si>
+    <t>397,39</t>
+  </si>
+  <si>
+    <t>5,61</t>
+  </si>
+  <si>
+    <t>586,23</t>
+  </si>
+  <si>
+    <t>451,77</t>
+  </si>
+  <si>
+    <t>306,64</t>
+  </si>
+  <si>
+    <t>42,56</t>
+  </si>
+  <si>
+    <t>30,00</t>
+  </si>
+  <si>
+    <t>397,08</t>
+  </si>
+  <si>
+    <t>207,94</t>
+  </si>
+  <si>
+    <t>158,16</t>
+  </si>
+  <si>
+    <t>215,26</t>
+  </si>
+  <si>
+    <t>27,60</t>
+  </si>
+  <si>
+    <t>137,22</t>
+  </si>
+  <si>
+    <t>209,38</t>
+  </si>
+  <si>
+    <t>344,96</t>
+  </si>
+  <si>
+    <t>16,20</t>
+  </si>
+  <si>
+    <t>5,88</t>
+  </si>
+  <si>
+    <t>333,75</t>
+  </si>
+  <si>
+    <t>60,82</t>
+  </si>
+  <si>
+    <t>617,04</t>
+  </si>
+  <si>
+    <t>172,26</t>
+  </si>
+  <si>
+    <t>158,00</t>
+  </si>
+  <si>
+    <t>18,00</t>
+  </si>
+  <si>
+    <t>143,00</t>
+  </si>
+  <si>
+    <t>228,00</t>
+  </si>
+  <si>
+    <t>97,57</t>
+  </si>
+  <si>
+    <t>39,42</t>
+  </si>
+  <si>
+    <t>355,52</t>
+  </si>
+  <si>
+    <t>153,37</t>
+  </si>
+  <si>
+    <t>215,96</t>
+  </si>
+  <si>
+    <t>323,05</t>
+  </si>
+  <si>
+    <t>252,98</t>
+  </si>
+  <si>
+    <t>406,64</t>
+  </si>
+  <si>
+    <t>201,68</t>
+  </si>
+  <si>
+    <t>55,90</t>
+  </si>
+  <si>
+    <t>337,84</t>
+  </si>
+  <si>
+    <t>38,98</t>
+  </si>
+  <si>
+    <t>92,46</t>
+  </si>
+  <si>
+    <t>54,72</t>
+  </si>
+  <si>
+    <t>458,06</t>
+  </si>
+  <si>
+    <t>4,96</t>
+  </si>
+  <si>
+    <t>196,46</t>
+  </si>
+  <si>
+    <t>255,30</t>
+  </si>
+  <si>
+    <t>214,66</t>
+  </si>
+  <si>
+    <t>51,34</t>
+  </si>
+  <si>
+    <t>150,42</t>
+  </si>
+  <si>
+    <t>130,05</t>
+  </si>
+  <si>
+    <t>256,03</t>
+  </si>
+  <si>
+    <t>108,11</t>
+  </si>
+  <si>
+    <t>203,80</t>
+  </si>
+  <si>
+    <t>172,50</t>
+  </si>
+  <si>
+    <t>511,14</t>
+  </si>
+  <si>
+    <t>89,00</t>
+  </si>
+  <si>
+    <t>54,28</t>
+  </si>
+  <si>
+    <t>161,68</t>
+  </si>
+  <si>
+    <t>187,06</t>
+  </si>
+  <si>
+    <t>572,99</t>
   </si>
 </sst>
 </file>
@@ -3792,7 +4383,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3806,6 +4397,8 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4121,7 +4714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE4913-4281-44EC-9895-A3BCDA934E02}">
-  <dimension ref="A1:E4058"/>
+  <dimension ref="A1:E4339"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -73113,6 +73706,4783 @@
         <v>46023</v>
       </c>
     </row>
+    <row r="4059" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4059" s="13">
+        <v>200295</v>
+      </c>
+      <c r="B4059" s="13" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C4059" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4059" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4059" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4060" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4060" s="14">
+        <v>32274</v>
+      </c>
+      <c r="B4060" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="C4060" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4060" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4060" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4061" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4061" s="13">
+        <v>420045</v>
+      </c>
+      <c r="B4061" s="13" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C4061" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D4061" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4061" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4062" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4062" s="14">
+        <v>61160</v>
+      </c>
+      <c r="B4062" s="14" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C4062" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D4062" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4062" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4063" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4063" s="13">
+        <v>21535</v>
+      </c>
+      <c r="B4063" s="13" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C4063" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4063" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4063" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4064" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4064" s="14">
+        <v>100332</v>
+      </c>
+      <c r="B4064" s="14" t="s">
+        <v>857</v>
+      </c>
+      <c r="C4064" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D4064" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4064" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4065" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4065" s="13">
+        <v>200231</v>
+      </c>
+      <c r="B4065" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4065" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D4065" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4065" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4066" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4066" s="14">
+        <v>60663</v>
+      </c>
+      <c r="B4066" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4066" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4066" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4066" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4067" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4067" s="13">
+        <v>21478</v>
+      </c>
+      <c r="B4067" s="13" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C4067" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D4067" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4067" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4068" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4068" s="14">
+        <v>32134</v>
+      </c>
+      <c r="B4068" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4068" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D4068" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4068" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4069" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4069" s="13">
+        <v>61184</v>
+      </c>
+      <c r="B4069" s="13" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C4069" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4069" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4069" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4070" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4070" s="14">
+        <v>200599</v>
+      </c>
+      <c r="B4070" s="14" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C4070" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D4070" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4070" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4071" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4071" s="13">
+        <v>19238</v>
+      </c>
+      <c r="B4071" s="13" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C4071" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4071" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4071" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4072" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4072" s="14">
+        <v>42002</v>
+      </c>
+      <c r="B4072" s="14" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C4072" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4072" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4072" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4073" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4073" s="13">
+        <v>32471</v>
+      </c>
+      <c r="B4073" s="13" t="s">
+        <v>859</v>
+      </c>
+      <c r="C4073" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D4073" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4073" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4074" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4074" s="14">
+        <v>41986</v>
+      </c>
+      <c r="B4074" s="14" t="s">
+        <v>860</v>
+      </c>
+      <c r="C4074" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D4074" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4074" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4075" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4075" s="13">
+        <v>61148</v>
+      </c>
+      <c r="B4075" s="13" t="s">
+        <v>822</v>
+      </c>
+      <c r="C4075" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4075" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E4075" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4076" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4076" s="14">
+        <v>2075</v>
+      </c>
+      <c r="B4076" s="14" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C4076" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4076" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4076" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4077" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4077" s="13">
+        <v>31969</v>
+      </c>
+      <c r="B4077" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4077" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D4077" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4077" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4078" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4078" s="14">
+        <v>21450</v>
+      </c>
+      <c r="B4078" s="14" t="s">
+        <v>642</v>
+      </c>
+      <c r="C4078" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4078" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4078" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4079" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4079" s="13">
+        <v>200475</v>
+      </c>
+      <c r="B4079" s="13" t="s">
+        <v>643</v>
+      </c>
+      <c r="C4079" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D4079" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4079" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4080" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4080" s="14">
+        <v>200264</v>
+      </c>
+      <c r="B4080" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4080" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D4080" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4080" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4081" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4081" s="13">
+        <v>643</v>
+      </c>
+      <c r="B4081" s="13" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C4081" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4081" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4081" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4082" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4082" s="14">
+        <v>61026</v>
+      </c>
+      <c r="B4082" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4082" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4082" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4082" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4083" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4083" s="13">
+        <v>210052</v>
+      </c>
+      <c r="B4083" s="13" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C4083" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D4083" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4083" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4084" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4084" s="14">
+        <v>210114</v>
+      </c>
+      <c r="B4084" s="14" t="s">
+        <v>993</v>
+      </c>
+      <c r="C4084" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D4084" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4084" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4085" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4085" s="13">
+        <v>60698</v>
+      </c>
+      <c r="B4085" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4085" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4085" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4085" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4086" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4086" s="14">
+        <v>2729</v>
+      </c>
+      <c r="B4086" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="C4086" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D4086" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4086" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4087" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4087" s="13">
+        <v>420026</v>
+      </c>
+      <c r="B4087" s="13" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C4087" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D4087" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4087" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4088" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4088" s="14">
+        <v>60898</v>
+      </c>
+      <c r="B4088" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4088" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4088" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4088" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4089" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4089" s="13">
+        <v>200198</v>
+      </c>
+      <c r="B4089" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4089" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4089" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4089" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4090" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4090" s="14">
+        <v>200602</v>
+      </c>
+      <c r="B4090" s="14" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C4090" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4090" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4090" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4091" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4091" s="13">
+        <v>21517</v>
+      </c>
+      <c r="B4091" s="13" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C4091" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4091" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4091" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4092" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4092" s="14">
+        <v>2946</v>
+      </c>
+      <c r="B4092" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4092" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4092" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4092" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4093" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4093" s="13">
+        <v>41511</v>
+      </c>
+      <c r="B4093" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4093" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4093" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4093" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4094" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4094" s="14">
+        <v>31017</v>
+      </c>
+      <c r="B4094" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4094" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4094" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4094" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4095" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4095" s="13">
+        <v>19337</v>
+      </c>
+      <c r="B4095" s="13" t="s">
+        <v>995</v>
+      </c>
+      <c r="C4095" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D4095" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4095" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4096" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4096" s="14">
+        <v>19275</v>
+      </c>
+      <c r="B4096" s="14" t="s">
+        <v>519</v>
+      </c>
+      <c r="C4096" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4096" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4096" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4097" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4097" s="13">
+        <v>21588</v>
+      </c>
+      <c r="B4097" s="13" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C4097" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D4097" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4097" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4098" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4098" s="14">
+        <v>19321</v>
+      </c>
+      <c r="B4098" s="14" t="s">
+        <v>863</v>
+      </c>
+      <c r="C4098" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D4098" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4098" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4099" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4099" s="13">
+        <v>220034</v>
+      </c>
+      <c r="B4099" s="13" t="s">
+        <v>657</v>
+      </c>
+      <c r="C4099" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D4099" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4099" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4100" s="14">
+        <v>31699</v>
+      </c>
+      <c r="B4100" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4100" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4100" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4100" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4101" s="13">
+        <v>19262</v>
+      </c>
+      <c r="B4101" s="13" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C4101" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D4101" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4101" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4102" s="14">
+        <v>200548</v>
+      </c>
+      <c r="B4102" s="14" t="s">
+        <v>999</v>
+      </c>
+      <c r="C4102" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D4102" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4102" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4103" s="13">
+        <v>41471</v>
+      </c>
+      <c r="B4103" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="C4103" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4103" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4103" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4104" s="14">
+        <v>200636</v>
+      </c>
+      <c r="B4104" s="14" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C4104" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4104" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4104" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4105" s="13">
+        <v>41969</v>
+      </c>
+      <c r="B4105" s="13" t="s">
+        <v>522</v>
+      </c>
+      <c r="C4105" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D4105" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4105" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4106" s="14">
+        <v>210053</v>
+      </c>
+      <c r="B4106" s="14" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C4106" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D4106" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4106" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4107" s="13">
+        <v>41883</v>
+      </c>
+      <c r="B4107" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="C4107" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4107" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4107" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4108" s="14">
+        <v>41462</v>
+      </c>
+      <c r="B4108" s="14" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C4108" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4108" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E4108" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4109" s="13">
+        <v>21211</v>
+      </c>
+      <c r="B4109" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4109" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4109" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4109" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4110" s="14">
+        <v>21518</v>
+      </c>
+      <c r="B4110" s="14" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C4110" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D4110" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4110" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4111" s="13">
+        <v>61173</v>
+      </c>
+      <c r="B4111" s="13" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C4111" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4111" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4111" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4112" s="14">
+        <v>31380</v>
+      </c>
+      <c r="B4112" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4112" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D4112" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4112" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4113" s="13">
+        <v>21498</v>
+      </c>
+      <c r="B4113" s="13" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C4113" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4113" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4113" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4114" s="14">
+        <v>21551</v>
+      </c>
+      <c r="B4114" s="14" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C4114" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D4114" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4114" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4115" s="13">
+        <v>220035</v>
+      </c>
+      <c r="B4115" s="13" t="s">
+        <v>525</v>
+      </c>
+      <c r="C4115" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D4115" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4115" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4116" s="14">
+        <v>32535</v>
+      </c>
+      <c r="B4116" s="14" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C4116" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D4116" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4116" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4117" s="13">
+        <v>61193</v>
+      </c>
+      <c r="B4117" s="13" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C4117" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D4117" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4117" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4118" s="14">
+        <v>61191</v>
+      </c>
+      <c r="B4118" s="14" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C4118" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4118" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4118" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4119" s="13">
+        <v>32430</v>
+      </c>
+      <c r="B4119" s="13" t="s">
+        <v>925</v>
+      </c>
+      <c r="C4119" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4119" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4119" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4120" s="14">
+        <v>2718</v>
+      </c>
+      <c r="B4120" s="14" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C4120" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4120" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4120" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4121" s="13">
+        <v>420016</v>
+      </c>
+      <c r="B4121" s="13" t="s">
+        <v>927</v>
+      </c>
+      <c r="C4121" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D4121" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4121" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4122" s="14">
+        <v>220037</v>
+      </c>
+      <c r="B4122" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4122" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D4122" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4122" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4123" s="13">
+        <v>220092</v>
+      </c>
+      <c r="B4123" s="13" t="s">
+        <v>667</v>
+      </c>
+      <c r="C4123" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D4123" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4123" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4124" s="14">
+        <v>32487</v>
+      </c>
+      <c r="B4124" s="14" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C4124" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4124" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4124" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4125" s="13">
+        <v>21573</v>
+      </c>
+      <c r="B4125" s="13" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C4125" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4125" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4125" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4126" s="14">
+        <v>100347</v>
+      </c>
+      <c r="B4126" s="14" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C4126" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D4126" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4126" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4127" s="13">
+        <v>2911</v>
+      </c>
+      <c r="B4127" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4127" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4127" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4127" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4128" s="14">
+        <v>61186</v>
+      </c>
+      <c r="B4128" s="14" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C4128" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4128" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4128" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4129" s="13">
+        <v>41864</v>
+      </c>
+      <c r="B4129" s="13" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C4129" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4129" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E4129" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4130" s="14">
+        <v>100280</v>
+      </c>
+      <c r="B4130" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="C4130" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4130" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4130" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4131" s="13">
+        <v>19298</v>
+      </c>
+      <c r="B4131" s="13" t="s">
+        <v>827</v>
+      </c>
+      <c r="C4131" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D4131" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4131" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4132" s="14">
+        <v>61046</v>
+      </c>
+      <c r="B4132" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4132" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D4132" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4132" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4133" s="13">
+        <v>2976</v>
+      </c>
+      <c r="B4133" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4133" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4133" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4133" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4134" s="14">
+        <v>2086</v>
+      </c>
+      <c r="B4134" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="C4134" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4134" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4134" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4135" s="13">
+        <v>64</v>
+      </c>
+      <c r="B4135" s="13" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C4135" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D4135" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4135" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4136" s="14">
+        <v>220033</v>
+      </c>
+      <c r="B4136" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="C4136" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D4136" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4136" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4137" s="13">
+        <v>19348</v>
+      </c>
+      <c r="B4137" s="13" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C4137" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4137" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4137" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4138" s="14">
+        <v>90913</v>
+      </c>
+      <c r="B4138" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="C4138" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4138" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4138" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4139" s="13">
+        <v>32438</v>
+      </c>
+      <c r="B4139" s="13" t="s">
+        <v>464</v>
+      </c>
+      <c r="C4139" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D4139" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4139" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4140" s="14">
+        <v>220046</v>
+      </c>
+      <c r="B4140" s="14" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C4140" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D4140" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4140" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4141" s="13">
+        <v>100273</v>
+      </c>
+      <c r="B4141" s="13" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C4141" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D4141" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4141" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4142" s="14">
+        <v>32297</v>
+      </c>
+      <c r="B4142" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="C4142" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4142" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4142" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4143" s="13">
+        <v>200514</v>
+      </c>
+      <c r="B4143" s="13" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C4143" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D4143" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4143" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4144" s="14">
+        <v>32217</v>
+      </c>
+      <c r="B4144" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="C4144" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D4144" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4144" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4145" s="13">
+        <v>200496</v>
+      </c>
+      <c r="B4145" s="13" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C4145" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D4145" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4145" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4146" s="14">
+        <v>32441</v>
+      </c>
+      <c r="B4146" s="14" t="s">
+        <v>872</v>
+      </c>
+      <c r="C4146" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4146" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4146" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4147" s="13">
+        <v>200240</v>
+      </c>
+      <c r="B4147" s="13" t="s">
+        <v>931</v>
+      </c>
+      <c r="C4147" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4147" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4147" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4148" s="14">
+        <v>220038</v>
+      </c>
+      <c r="B4148" s="14" t="s">
+        <v>550</v>
+      </c>
+      <c r="C4148" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D4148" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4148" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4149" s="13">
+        <v>200617</v>
+      </c>
+      <c r="B4149" s="13" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C4149" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D4149" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4149" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4150" s="14">
+        <v>21221</v>
+      </c>
+      <c r="B4150" s="14" t="s">
+        <v>466</v>
+      </c>
+      <c r="C4150" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D4150" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4150" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4151" s="13">
+        <v>32480</v>
+      </c>
+      <c r="B4151" s="13" t="s">
+        <v>932</v>
+      </c>
+      <c r="C4151" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D4151" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4151" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4152" s="14">
+        <v>100281</v>
+      </c>
+      <c r="B4152" s="14" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C4152" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D4152" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4152" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4153" s="13">
+        <v>61196</v>
+      </c>
+      <c r="B4153" s="13" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C4153" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4153" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4153" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4154" s="14">
+        <v>31776</v>
+      </c>
+      <c r="B4154" s="14" t="s">
+        <v>554</v>
+      </c>
+      <c r="C4154" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4154" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4154" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4155" s="13">
+        <v>210115</v>
+      </c>
+      <c r="B4155" s="13" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C4155" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D4155" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4155" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4156" s="14">
+        <v>60721</v>
+      </c>
+      <c r="B4156" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4156" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D4156" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4156" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4157" s="13">
+        <v>420059</v>
+      </c>
+      <c r="B4157" s="13" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C4157" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D4157" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4157" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4158" s="14">
+        <v>21363</v>
+      </c>
+      <c r="B4158" s="14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C4158" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4158" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4158" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4159" s="13">
+        <v>21102</v>
+      </c>
+      <c r="B4159" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="C4159" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4159" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4159" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4160" s="14">
+        <v>200361</v>
+      </c>
+      <c r="B4160" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4160" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4160" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4160" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4161" s="13">
+        <v>21301</v>
+      </c>
+      <c r="B4161" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4161" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4161" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4161" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4162" s="14">
+        <v>21499</v>
+      </c>
+      <c r="B4162" s="14" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C4162" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D4162" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4162" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4163" s="13">
+        <v>21378</v>
+      </c>
+      <c r="B4163" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C4163" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D4163" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4163" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4164" s="14">
+        <v>100167</v>
+      </c>
+      <c r="B4164" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="C4164" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D4164" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4164" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4165" s="13">
+        <v>41306</v>
+      </c>
+      <c r="B4165" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="C4165" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D4165" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4165" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4166" s="14">
+        <v>200135</v>
+      </c>
+      <c r="B4166" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="C4166" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D4166" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4166" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4167" s="13">
+        <v>210116</v>
+      </c>
+      <c r="B4167" s="13" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C4167" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4167" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4167" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4168" s="14">
+        <v>60827</v>
+      </c>
+      <c r="B4168" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4168" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D4168" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4168" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4169" s="13">
+        <v>32488</v>
+      </c>
+      <c r="B4169" s="13" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C4169" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4169" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4169" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4170" s="14">
+        <v>200328</v>
+      </c>
+      <c r="B4170" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="C4170" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4170" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4170" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4171" s="13">
+        <v>200440</v>
+      </c>
+      <c r="B4171" s="13" t="s">
+        <v>879</v>
+      </c>
+      <c r="C4171" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D4171" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4171" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4172" s="14">
+        <v>32369</v>
+      </c>
+      <c r="B4172" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4172" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4172" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4172" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4173" s="13">
+        <v>32361</v>
+      </c>
+      <c r="B4173" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C4173" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D4173" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4173" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4174" s="14">
+        <v>200086</v>
+      </c>
+      <c r="B4174" s="14" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C4174" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4174" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4174" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4175" s="13">
+        <v>31974</v>
+      </c>
+      <c r="B4175" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4175" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D4175" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4175" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4176" s="14">
+        <v>2493</v>
+      </c>
+      <c r="B4176" s="14" t="s">
+        <v>941</v>
+      </c>
+      <c r="C4176" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4176" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4176" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4177" s="13">
+        <v>32360</v>
+      </c>
+      <c r="B4177" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4177" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4177" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4177" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4178" s="14">
+        <v>200622</v>
+      </c>
+      <c r="B4178" s="14" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C4178" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D4178" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4178" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4179" s="13">
+        <v>420065</v>
+      </c>
+      <c r="B4179" s="13" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C4179" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D4179" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4179" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4180" s="14">
+        <v>100106</v>
+      </c>
+      <c r="B4180" s="14" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C4180" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4180" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4180" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4181" s="13">
+        <v>1853</v>
+      </c>
+      <c r="B4181" s="13" t="s">
+        <v>945</v>
+      </c>
+      <c r="C4181" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4181" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4181" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4182" s="14">
+        <v>21092</v>
+      </c>
+      <c r="B4182" s="14" t="s">
+        <v>880</v>
+      </c>
+      <c r="C4182" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D4182" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4182" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4183" s="13">
+        <v>32280</v>
+      </c>
+      <c r="B4183" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4183" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4183" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4183" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4184" s="14">
+        <v>200577</v>
+      </c>
+      <c r="B4184" s="14" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C4184" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4184" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4184" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4185" s="13">
+        <v>19204</v>
+      </c>
+      <c r="B4185" s="13" t="s">
+        <v>557</v>
+      </c>
+      <c r="C4185" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4185" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4185" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4186" s="14">
+        <v>41664</v>
+      </c>
+      <c r="B4186" s="14" t="s">
+        <v>946</v>
+      </c>
+      <c r="C4186" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4186" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4186" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4187" s="13">
+        <v>61170</v>
+      </c>
+      <c r="B4187" s="13" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C4187" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D4187" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4187" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4188" s="14">
+        <v>19340</v>
+      </c>
+      <c r="B4188" s="14" t="s">
+        <v>947</v>
+      </c>
+      <c r="C4188" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D4188" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4188" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4189" s="13">
+        <v>21434</v>
+      </c>
+      <c r="B4189" s="13" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C4189" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D4189" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4189" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4190" s="14">
+        <v>61187</v>
+      </c>
+      <c r="B4190" s="14" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C4190" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4190" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4190" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4191" s="13">
+        <v>61126</v>
+      </c>
+      <c r="B4191" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="C4191" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D4191" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4191" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4192" s="14">
+        <v>19246</v>
+      </c>
+      <c r="B4192" s="14" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C4192" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4192" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4192" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4193" s="13">
+        <v>220014</v>
+      </c>
+      <c r="B4193" s="13" t="s">
+        <v>560</v>
+      </c>
+      <c r="C4193" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D4193" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4193" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4194" s="14">
+        <v>210118</v>
+      </c>
+      <c r="B4194" s="14" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C4194" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4194" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4194" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4195" s="13">
+        <v>21544</v>
+      </c>
+      <c r="B4195" s="13" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C4195" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D4195" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4195" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4196" s="14">
+        <v>41679</v>
+      </c>
+      <c r="B4196" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4196" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4196" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E4196" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4197" s="13">
+        <v>19332</v>
+      </c>
+      <c r="B4197" s="13" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C4197" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4197" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4197" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4198" s="14">
+        <v>2812</v>
+      </c>
+      <c r="B4198" s="14" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C4198" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D4198" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4198" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4199" s="13">
+        <v>220002</v>
+      </c>
+      <c r="B4199" s="13" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C4199" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D4199" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4199" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4200" s="14">
+        <v>200067</v>
+      </c>
+      <c r="B4200" s="14" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C4200" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4200" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4200" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4201" s="13">
+        <v>1210</v>
+      </c>
+      <c r="B4201" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4201" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4201" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4201" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4202" s="14">
+        <v>2255</v>
+      </c>
+      <c r="B4202" s="14" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C4202" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D4202" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4202" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4203" s="13">
+        <v>200426</v>
+      </c>
+      <c r="B4203" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="C4203" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D4203" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4203" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4204" s="14">
+        <v>220045</v>
+      </c>
+      <c r="B4204" s="14" t="s">
+        <v>716</v>
+      </c>
+      <c r="C4204" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D4204" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4204" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4205" s="13">
+        <v>41849</v>
+      </c>
+      <c r="B4205" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C4205" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4205" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4205" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4206" s="14">
+        <v>60344</v>
+      </c>
+      <c r="B4206" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="C4206" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D4206" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4206" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4207" s="13">
+        <v>21553</v>
+      </c>
+      <c r="B4207" s="13" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C4207" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4207" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4207" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4208" s="14">
+        <v>200638</v>
+      </c>
+      <c r="B4208" s="14" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C4208" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D4208" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4208" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4209" s="13">
+        <v>200387</v>
+      </c>
+      <c r="B4209" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4209" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4209" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4209" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4210" s="14">
+        <v>200363</v>
+      </c>
+      <c r="B4210" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="C4210" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4210" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4210" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4211" s="13">
+        <v>61104</v>
+      </c>
+      <c r="B4211" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4211" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4211" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E4211" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4212" s="14">
+        <v>21239</v>
+      </c>
+      <c r="B4212" s="14" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C4212" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4212" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4212" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4213" s="13">
+        <v>200601</v>
+      </c>
+      <c r="B4213" s="13" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C4213" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4213" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4213" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4214" s="14">
+        <v>32481</v>
+      </c>
+      <c r="B4214" s="14" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C4214" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4214" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4214" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4215" s="13">
+        <v>200639</v>
+      </c>
+      <c r="B4215" s="13" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C4215" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D4215" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4215" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4216" s="14">
+        <v>21184</v>
+      </c>
+      <c r="B4216" s="14" t="s">
+        <v>882</v>
+      </c>
+      <c r="C4216" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4216" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4216" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4217" s="13">
+        <v>200160</v>
+      </c>
+      <c r="B4217" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="C4217" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D4217" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4217" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4218" s="14">
+        <v>220021</v>
+      </c>
+      <c r="B4218" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="C4218" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D4218" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4218" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4219" s="13">
+        <v>19315</v>
+      </c>
+      <c r="B4219" s="13" t="s">
+        <v>883</v>
+      </c>
+      <c r="C4219" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D4219" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4219" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4220" s="14">
+        <v>200545</v>
+      </c>
+      <c r="B4220" s="14" t="s">
+        <v>884</v>
+      </c>
+      <c r="C4220" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D4220" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4220" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4221" s="13">
+        <v>200499</v>
+      </c>
+      <c r="B4221" s="13" t="s">
+        <v>885</v>
+      </c>
+      <c r="C4221" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D4221" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4221" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4222" s="14">
+        <v>19235</v>
+      </c>
+      <c r="B4222" s="14" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C4222" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4222" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4222" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4223" s="13">
+        <v>19316</v>
+      </c>
+      <c r="B4223" s="13" t="s">
+        <v>887</v>
+      </c>
+      <c r="C4223" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D4223" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4223" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4224" s="14">
+        <v>31727</v>
+      </c>
+      <c r="B4224" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="C4224" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D4224" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4224" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4225" s="13">
+        <v>420069</v>
+      </c>
+      <c r="B4225" s="13" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C4225" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D4225" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4225" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4226" s="14">
+        <v>200018</v>
+      </c>
+      <c r="B4226" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4226" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D4226" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4226" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4227" s="13">
+        <v>41402</v>
+      </c>
+      <c r="B4227" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="C4227" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D4227" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4227" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4228" s="14">
+        <v>200506</v>
+      </c>
+      <c r="B4228" s="14" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C4228" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D4228" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4228" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4229" s="13">
+        <v>60969</v>
+      </c>
+      <c r="B4229" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4229" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D4229" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4229" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4230" s="14">
+        <v>200632</v>
+      </c>
+      <c r="B4230" s="14" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C4230" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D4230" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4230" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4231" s="13">
+        <v>210110</v>
+      </c>
+      <c r="B4231" s="13" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C4231" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D4231" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4231" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4232" s="14">
+        <v>200199</v>
+      </c>
+      <c r="B4232" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4232" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D4232" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4232" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4233" s="13">
+        <v>21481</v>
+      </c>
+      <c r="B4233" s="13" t="s">
+        <v>955</v>
+      </c>
+      <c r="C4233" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4233" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4233" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4234" s="14">
+        <v>200536</v>
+      </c>
+      <c r="B4234" s="14" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C4234" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4234" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4234" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4235" s="13">
+        <v>32355</v>
+      </c>
+      <c r="B4235" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4235" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D4235" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4235" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4236" s="14">
+        <v>220039</v>
+      </c>
+      <c r="B4236" s="14" t="s">
+        <v>957</v>
+      </c>
+      <c r="C4236" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D4236" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4236" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4237" s="13">
+        <v>32446</v>
+      </c>
+      <c r="B4237" s="13" t="s">
+        <v>573</v>
+      </c>
+      <c r="C4237" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4237" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4237" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4238" s="14">
+        <v>200507</v>
+      </c>
+      <c r="B4238" s="14" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C4238" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D4238" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4238" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4239" s="13">
+        <v>210032</v>
+      </c>
+      <c r="B4239" s="13" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C4239" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D4239" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4239" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4240" s="14">
+        <v>100226</v>
+      </c>
+      <c r="B4240" s="14" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C4240" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D4240" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4240" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4241" s="13">
+        <v>200020</v>
+      </c>
+      <c r="B4241" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4241" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D4241" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4241" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4242" s="14">
+        <v>60745</v>
+      </c>
+      <c r="B4242" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4242" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4242" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4242" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4243" s="13">
+        <v>21584</v>
+      </c>
+      <c r="B4243" s="13" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C4243" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4243" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4243" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4244" s="14">
+        <v>22022</v>
+      </c>
+      <c r="B4244" s="14" t="s">
+        <v>576</v>
+      </c>
+      <c r="C4244" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D4244" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4244" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4245" s="13">
+        <v>21576</v>
+      </c>
+      <c r="B4245" s="13" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C4245" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4245" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4245" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4246" s="14">
+        <v>21354</v>
+      </c>
+      <c r="B4246" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4246" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4246" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4246" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4247" s="13">
+        <v>61065</v>
+      </c>
+      <c r="B4247" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4247" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4247" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4247" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4248" s="14">
+        <v>41445</v>
+      </c>
+      <c r="B4248" s="14" t="s">
+        <v>844</v>
+      </c>
+      <c r="C4248" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4248" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4248" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4249" s="13">
+        <v>41997</v>
+      </c>
+      <c r="B4249" s="13" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C4249" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4249" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4249" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4250" s="14">
+        <v>60912</v>
+      </c>
+      <c r="B4250" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4250" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4250" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4250" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4251" s="13">
+        <v>60867</v>
+      </c>
+      <c r="B4251" s="13" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C4251" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D4251" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4251" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4252" s="14">
+        <v>220008</v>
+      </c>
+      <c r="B4252" s="14" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C4252" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4252" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4252" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4253" s="13">
+        <v>220013</v>
+      </c>
+      <c r="B4253" s="13" t="s">
+        <v>845</v>
+      </c>
+      <c r="C4253" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D4253" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4253" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4254" s="14">
+        <v>32498</v>
+      </c>
+      <c r="B4254" s="14" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C4254" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D4254" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4254" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4255" s="13">
+        <v>210048</v>
+      </c>
+      <c r="B4255" s="13" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C4255" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D4255" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4255" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4256" s="14">
+        <v>90427</v>
+      </c>
+      <c r="B4256" s="14" t="s">
+        <v>323</v>
+      </c>
+      <c r="C4256" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4256" t="s">
+        <v>1391</v>
+      </c>
+      <c r="E4256" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4257" s="13">
+        <v>19300</v>
+      </c>
+      <c r="B4257" s="13" t="s">
+        <v>846</v>
+      </c>
+      <c r="C4257" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D4257" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4257" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4258" s="14">
+        <v>200278</v>
+      </c>
+      <c r="B4258" s="14" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C4258" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4258" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4258" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4259" s="13">
+        <v>61188</v>
+      </c>
+      <c r="B4259" s="13" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C4259" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D4259" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4259" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4260" s="14">
+        <v>60973</v>
+      </c>
+      <c r="B4260" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="C4260" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D4260" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4260" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4261" s="13">
+        <v>220041</v>
+      </c>
+      <c r="B4261" s="13" t="s">
+        <v>893</v>
+      </c>
+      <c r="C4261" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D4261" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4261" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4262" s="14">
+        <v>2824</v>
+      </c>
+      <c r="B4262" s="14" t="s">
+        <v>487</v>
+      </c>
+      <c r="C4262" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4262" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4262" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4263" s="13">
+        <v>200191</v>
+      </c>
+      <c r="B4263" s="13" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C4263" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4263" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E4263" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4264" s="14">
+        <v>200574</v>
+      </c>
+      <c r="B4264" s="14" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C4264" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D4264" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4264" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4265" s="13">
+        <v>2850</v>
+      </c>
+      <c r="B4265" s="13" t="s">
+        <v>962</v>
+      </c>
+      <c r="C4265" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4265" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4265" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4266" s="14">
+        <v>61097</v>
+      </c>
+      <c r="B4266" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4266" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D4266" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4266" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4267" s="13">
+        <v>200535</v>
+      </c>
+      <c r="B4267" s="13" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C4267" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D4267" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4267" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4268" s="14">
+        <v>200152</v>
+      </c>
+      <c r="B4268" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="C4268" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D4268" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4268" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4269" s="13">
+        <v>200580</v>
+      </c>
+      <c r="B4269" s="13" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C4269" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D4269" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4269" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4270" s="14">
+        <v>32398</v>
+      </c>
+      <c r="B4270" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4270" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4270" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4270" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4271" s="13">
+        <v>220001</v>
+      </c>
+      <c r="B4271" s="13" t="s">
+        <v>964</v>
+      </c>
+      <c r="C4271" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4271" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4271" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4272" s="14">
+        <v>2781</v>
+      </c>
+      <c r="B4272" s="14" t="s">
+        <v>894</v>
+      </c>
+      <c r="C4272" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4272" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4272" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4273" s="13">
+        <v>210049</v>
+      </c>
+      <c r="B4273" s="13" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C4273" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D4273" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4273" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4274" s="14">
+        <v>200430</v>
+      </c>
+      <c r="B4274" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="C4274" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D4274" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4274" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4275" s="13">
+        <v>21529</v>
+      </c>
+      <c r="B4275" s="13" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C4275" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4275" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4275" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4276" s="14">
+        <v>19278</v>
+      </c>
+      <c r="B4276" s="14" t="s">
+        <v>587</v>
+      </c>
+      <c r="C4276" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D4276" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4276" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4277" s="13">
+        <v>210099</v>
+      </c>
+      <c r="B4277" s="13" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C4277" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D4277" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4277" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4278" s="14">
+        <v>200378</v>
+      </c>
+      <c r="B4278" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="C4278" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D4278" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4278" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4279" s="13">
+        <v>21356</v>
+      </c>
+      <c r="B4279" s="13" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C4279" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4279" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4279" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4280" s="14">
+        <v>90201</v>
+      </c>
+      <c r="B4280" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="C4280" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4280" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E4280" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4281" s="13">
+        <v>21524</v>
+      </c>
+      <c r="B4281" s="13" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C4281" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4281" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4281" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4282" s="14">
+        <v>61181</v>
+      </c>
+      <c r="B4282" s="14" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C4282" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D4282" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4282" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4283" s="13">
+        <v>396</v>
+      </c>
+      <c r="B4283" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4283" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D4283" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4283" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4284" s="14">
+        <v>19326</v>
+      </c>
+      <c r="B4284" s="14" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C4284" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4284" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4284" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4285" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4285" s="13">
+        <v>19296</v>
+      </c>
+      <c r="B4285" s="13" t="s">
+        <v>847</v>
+      </c>
+      <c r="C4285" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D4285" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4285" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4286" s="14">
+        <v>41468</v>
+      </c>
+      <c r="B4286" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="C4286" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D4286" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4286" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4287" s="13">
+        <v>32426</v>
+      </c>
+      <c r="B4287" s="13" t="s">
+        <v>771</v>
+      </c>
+      <c r="C4287" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4287" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4287" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4288" s="14">
+        <v>60987</v>
+      </c>
+      <c r="B4288" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4288" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4288" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4288" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4289" s="13">
+        <v>32429</v>
+      </c>
+      <c r="B4289" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="C4289" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D4289" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4289" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4290" s="14">
+        <v>32461</v>
+      </c>
+      <c r="B4290" s="14" t="s">
+        <v>597</v>
+      </c>
+      <c r="C4290" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4290" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4290" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4291" s="13">
+        <v>210109</v>
+      </c>
+      <c r="B4291" s="13" t="s">
+        <v>968</v>
+      </c>
+      <c r="C4291" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D4291" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4291" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4292" s="14">
+        <v>114</v>
+      </c>
+      <c r="B4292" s="14" t="s">
+        <v>776</v>
+      </c>
+      <c r="C4292" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4292" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4292" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4293" s="13">
+        <v>32474</v>
+      </c>
+      <c r="B4293" s="13" t="s">
+        <v>970</v>
+      </c>
+      <c r="C4293" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D4293" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4293" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4294" s="14">
+        <v>21495</v>
+      </c>
+      <c r="B4294" s="14" t="s">
+        <v>850</v>
+      </c>
+      <c r="C4294" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4294" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4294" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4295" s="13">
+        <v>220017</v>
+      </c>
+      <c r="B4295" s="13" t="s">
+        <v>601</v>
+      </c>
+      <c r="C4295" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D4295" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4295" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4296" s="14">
+        <v>21559</v>
+      </c>
+      <c r="B4296" s="14" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C4296" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D4296" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4296" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4297" s="13">
+        <v>200094</v>
+      </c>
+      <c r="B4297" s="13" t="s">
+        <v>412</v>
+      </c>
+      <c r="C4297" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D4297" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4297" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4298" s="14">
+        <v>31414</v>
+      </c>
+      <c r="B4298" s="14" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C4298" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4298" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4298" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4299" s="13">
+        <v>420042</v>
+      </c>
+      <c r="B4299" s="13" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C4299" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D4299" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4299" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4300" s="14">
+        <v>210041</v>
+      </c>
+      <c r="B4300" s="14" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C4300" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D4300" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4300" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4301" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4301" s="13">
+        <v>200105</v>
+      </c>
+      <c r="B4301" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="C4301" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D4301" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4301" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4302" s="14">
+        <v>21277</v>
+      </c>
+      <c r="B4302" s="14" t="s">
+        <v>852</v>
+      </c>
+      <c r="C4302" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D4302" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4302" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4303" s="13">
+        <v>21490</v>
+      </c>
+      <c r="B4303" s="13" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C4303" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4303" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4303" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4304" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4304" s="14">
+        <v>61122</v>
+      </c>
+      <c r="B4304" s="14" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C4304" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4304" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4304" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4305" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4305" s="13">
+        <v>200258</v>
+      </c>
+      <c r="B4305" s="13" t="s">
+        <v>501</v>
+      </c>
+      <c r="C4305" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4305" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4305" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4306" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4306" s="14">
+        <v>200346</v>
+      </c>
+      <c r="B4306" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4306" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D4306" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4306" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4307" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4307" s="13">
+        <v>200277</v>
+      </c>
+      <c r="B4307" s="13" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C4307" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4307" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4307" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4308" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4308" s="14">
+        <v>2204</v>
+      </c>
+      <c r="B4308" s="14" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C4308" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4308" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4308" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4309" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4309" s="13">
+        <v>2559</v>
+      </c>
+      <c r="B4309" s="13" t="s">
+        <v>975</v>
+      </c>
+      <c r="C4309" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4309" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4309" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4310" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4310" s="14">
+        <v>220086</v>
+      </c>
+      <c r="B4310" s="14" t="s">
+        <v>789</v>
+      </c>
+      <c r="C4310" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D4310" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4310" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4311" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4311" s="13">
+        <v>32318</v>
+      </c>
+      <c r="B4311" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4311" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4311" t="s">
+        <v>1416</v>
+      </c>
+      <c r="E4311" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4312" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4312" s="14">
+        <v>32395</v>
+      </c>
+      <c r="B4312" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4312" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4312" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4312" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4313" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4313" s="13">
+        <v>21556</v>
+      </c>
+      <c r="B4313" s="13" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C4313" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D4313" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4313" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4314" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4314" s="14">
+        <v>200452</v>
+      </c>
+      <c r="B4314" s="14" t="s">
+        <v>793</v>
+      </c>
+      <c r="C4314" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D4314" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4314" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4315" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4315" s="13">
+        <v>2921</v>
+      </c>
+      <c r="B4315" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="C4315" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D4315" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4315" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4316" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4316" s="14">
+        <v>21482</v>
+      </c>
+      <c r="B4316" s="14" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C4316" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D4316" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4316" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4317" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4317" s="13">
+        <v>200008</v>
+      </c>
+      <c r="B4317" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="C4317" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D4317" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4317" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4318" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4318" s="14">
+        <v>41116</v>
+      </c>
+      <c r="B4318" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="C4318" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4318" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E4318" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4319" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4319" s="13">
+        <v>90850</v>
+      </c>
+      <c r="B4319" s="13" t="s">
+        <v>979</v>
+      </c>
+      <c r="C4319" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4319" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E4319" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4320" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4320" s="14">
+        <v>19320</v>
+      </c>
+      <c r="B4320" s="14" t="s">
+        <v>909</v>
+      </c>
+      <c r="C4320" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D4320" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4320" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4321" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4321" s="13">
+        <v>21358</v>
+      </c>
+      <c r="B4321" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="C4321" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4321" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4321" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4322" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4322" s="14">
+        <v>61164</v>
+      </c>
+      <c r="B4322" s="14" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C4322" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D4322" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4322" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4323" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4323" s="13">
+        <v>61119</v>
+      </c>
+      <c r="B4323" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="C4323" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4323" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4323" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4324" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4324" s="14">
+        <v>220048</v>
+      </c>
+      <c r="B4324" s="14" t="s">
+        <v>622</v>
+      </c>
+      <c r="C4324" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D4324" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4324" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4325" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4325" s="13">
+        <v>19329</v>
+      </c>
+      <c r="B4325" s="13" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C4325" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4325" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4325" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4326" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4326" s="14">
+        <v>32381</v>
+      </c>
+      <c r="B4326" s="14" t="s">
+        <v>623</v>
+      </c>
+      <c r="C4326" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4326" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4326" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4327" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4327" s="13">
+        <v>32462</v>
+      </c>
+      <c r="B4327" s="13" t="s">
+        <v>624</v>
+      </c>
+      <c r="C4327" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4327" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4327" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4328" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4328" s="14">
+        <v>31613</v>
+      </c>
+      <c r="B4328" s="14" t="s">
+        <v>625</v>
+      </c>
+      <c r="C4328" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4328" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4328" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4329" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4329" s="13">
+        <v>32052</v>
+      </c>
+      <c r="B4329" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4329" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4329" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4329" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4330" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4330" s="14">
+        <v>61056</v>
+      </c>
+      <c r="B4330" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4330" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4330" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4330" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4331" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4331" s="13">
+        <v>61112</v>
+      </c>
+      <c r="B4331" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4331" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D4331" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4331" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4332" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4332" s="14">
+        <v>200479</v>
+      </c>
+      <c r="B4332" s="14" t="s">
+        <v>812</v>
+      </c>
+      <c r="C4332" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D4332" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4332" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4333" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4333" s="13">
+        <v>42012</v>
+      </c>
+      <c r="B4333" s="13" t="s">
+        <v>983</v>
+      </c>
+      <c r="C4333" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D4333" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4333" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4334" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4334" s="14">
+        <v>32303</v>
+      </c>
+      <c r="B4334" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="C4334" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D4334" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4334" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4335" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4335" s="13">
+        <v>100324</v>
+      </c>
+      <c r="B4335" s="13" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C4335" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D4335" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4335" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4336" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4336" s="14">
+        <v>21247</v>
+      </c>
+      <c r="B4336" s="14" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C4336" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D4336" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4336" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4337" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4337" s="13">
+        <v>19249</v>
+      </c>
+      <c r="B4337" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C4337" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D4337" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4337" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4338" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4338" s="14">
+        <v>41404</v>
+      </c>
+      <c r="B4338" s="14" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C4338" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4338" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4338" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="4339" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4339" s="13">
+        <v>19257</v>
+      </c>
+      <c r="B4339" s="13" t="s">
+        <v>507</v>
+      </c>
+      <c r="C4339" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D4339" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4339" s="1">
+        <v>46054</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/Vales.xlsx
+++ b/data/Vales.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\Raio X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E545C846-B9F6-4D3A-AA2E-8F3A751865A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CE26FE-B66D-491D-8CE7-1C664AF8A526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E17B0997-73A2-49BF-8FD7-6792AA05DE7F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{E17B0997-73A2-49BF-8FD7-6792AA05DE7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$E$4680</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6284" uniqueCount="1657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7712" uniqueCount="1895">
   <si>
     <t>MATRICULA</t>
   </si>
@@ -5007,6 +5010,720 @@
   </si>
   <si>
     <t xml:space="preserve">WILLIAN SOUZA DOS SANTOS </t>
+  </si>
+  <si>
+    <t>176,66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALAN RODRIGUES BASTOS </t>
+  </si>
+  <si>
+    <t>49,76</t>
+  </si>
+  <si>
+    <t>ALDO RAFAEL SANTOS ROQUE DA SILVA</t>
+  </si>
+  <si>
+    <t>172,69</t>
+  </si>
+  <si>
+    <t>68,15</t>
+  </si>
+  <si>
+    <t>446,90</t>
+  </si>
+  <si>
+    <t>388,15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALVARO VIEIRA MATOS </t>
+  </si>
+  <si>
+    <t>252,59</t>
+  </si>
+  <si>
+    <t>ALYSSON WENDELL DOS PASSOS PEREIRA</t>
+  </si>
+  <si>
+    <t>593,03</t>
+  </si>
+  <si>
+    <t>180,20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREW JOSE DORIA </t>
+  </si>
+  <si>
+    <t>380,00</t>
+  </si>
+  <si>
+    <t>509,38</t>
+  </si>
+  <si>
+    <t>ANTONIO JOSE MEMORIA DE PAIVA  JUNIOR</t>
+  </si>
+  <si>
+    <t>21,21</t>
+  </si>
+  <si>
+    <t>ARIADINE DOS SANTOS MATIAS KRUGER</t>
+  </si>
+  <si>
+    <t>148,90</t>
+  </si>
+  <si>
+    <t>455,40</t>
+  </si>
+  <si>
+    <t>258,55</t>
+  </si>
+  <si>
+    <t>BRENO CORTÁCIO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>14,13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRUNO CORTACIO DOS SANTOS </t>
+  </si>
+  <si>
+    <t>BRUNO DELFINO MILLER</t>
+  </si>
+  <si>
+    <t>561,88</t>
+  </si>
+  <si>
+    <t>392,49</t>
+  </si>
+  <si>
+    <t>520,28</t>
+  </si>
+  <si>
+    <t>496,45</t>
+  </si>
+  <si>
+    <t>BRUNO VIANA SILVA</t>
+  </si>
+  <si>
+    <t>358,29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS ANDRE OLIVEIRA BELEM </t>
+  </si>
+  <si>
+    <t>312,72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS CRUZ XAVIER </t>
+  </si>
+  <si>
+    <t>598,42</t>
+  </si>
+  <si>
+    <t>50,28</t>
+  </si>
+  <si>
+    <t>451,20</t>
+  </si>
+  <si>
+    <t>58,65</t>
+  </si>
+  <si>
+    <t>CARLOS MAGNO MARQUES PEREIRA</t>
+  </si>
+  <si>
+    <t>36,70</t>
+  </si>
+  <si>
+    <t>95,87</t>
+  </si>
+  <si>
+    <t>CHRISTIAN OLIVEIRA ANDRE</t>
+  </si>
+  <si>
+    <t>201,75</t>
+  </si>
+  <si>
+    <t>259,91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAYTON PASSOS DA SILVA </t>
+  </si>
+  <si>
+    <t>7,06</t>
+  </si>
+  <si>
+    <t>335,42</t>
+  </si>
+  <si>
+    <t>CLEITON PEREIRA OLIVEIRA</t>
+  </si>
+  <si>
+    <t>239,54</t>
+  </si>
+  <si>
+    <t>DANIEL FERREIRA</t>
+  </si>
+  <si>
+    <t>351,62</t>
+  </si>
+  <si>
+    <t>248,11</t>
+  </si>
+  <si>
+    <t>46,73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANNY DE OLIVEIRA SILVA </t>
+  </si>
+  <si>
+    <t>DENILSON LOPES SENA</t>
+  </si>
+  <si>
+    <t>46,55</t>
+  </si>
+  <si>
+    <t>137,20</t>
+  </si>
+  <si>
+    <t>DIEGO BERNINI LOPES</t>
+  </si>
+  <si>
+    <t>114,96</t>
+  </si>
+  <si>
+    <t>81,87</t>
+  </si>
+  <si>
+    <t>130,30</t>
+  </si>
+  <si>
+    <t>376,64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUGLAS GUERRA CANTANHEDE </t>
+  </si>
+  <si>
+    <t>187,80</t>
+  </si>
+  <si>
+    <t>33,00</t>
+  </si>
+  <si>
+    <t>272,67</t>
+  </si>
+  <si>
+    <t>26,97</t>
+  </si>
+  <si>
+    <t>556,35</t>
+  </si>
+  <si>
+    <t>434,85</t>
+  </si>
+  <si>
+    <t>503,17</t>
+  </si>
+  <si>
+    <t>146,94</t>
+  </si>
+  <si>
+    <t>ELIO SKIBINSKI DE LIMA</t>
+  </si>
+  <si>
+    <t>ELISANGELA DE FREITAS</t>
+  </si>
+  <si>
+    <t>240,20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMILIO DONNANTUONI DA SILVA </t>
+  </si>
+  <si>
+    <t>79,85</t>
+  </si>
+  <si>
+    <t>290,00</t>
+  </si>
+  <si>
+    <t>155,95</t>
+  </si>
+  <si>
+    <t>ETISON PEDRO DA ROSA</t>
+  </si>
+  <si>
+    <t>248,42</t>
+  </si>
+  <si>
+    <t>41,85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVERSON ALVES FLORENTINO </t>
+  </si>
+  <si>
+    <t>3,34</t>
+  </si>
+  <si>
+    <t>406,33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FELIPE BETTIOL DE CASTRO </t>
+  </si>
+  <si>
+    <t>626,24</t>
+  </si>
+  <si>
+    <t>230,18</t>
+  </si>
+  <si>
+    <t>FERNANDO ELIAS DE CAMPOS</t>
+  </si>
+  <si>
+    <t>83,00</t>
+  </si>
+  <si>
+    <t>FERNANDO LUIZ GUANDALIN BARATTO</t>
+  </si>
+  <si>
+    <t>153,25</t>
+  </si>
+  <si>
+    <t>163,80</t>
+  </si>
+  <si>
+    <t>707,55</t>
+  </si>
+  <si>
+    <t>202,93</t>
+  </si>
+  <si>
+    <t>100,20</t>
+  </si>
+  <si>
+    <t>13,21</t>
+  </si>
+  <si>
+    <t>556,20</t>
+  </si>
+  <si>
+    <t>30,69</t>
+  </si>
+  <si>
+    <t>193,74</t>
+  </si>
+  <si>
+    <t>370,80</t>
+  </si>
+  <si>
+    <t>169,52</t>
+  </si>
+  <si>
+    <t>GUSTAVO FELIPE GODOI</t>
+  </si>
+  <si>
+    <t>583,41</t>
+  </si>
+  <si>
+    <t>420,00</t>
+  </si>
+  <si>
+    <t>128,17</t>
+  </si>
+  <si>
+    <t>78,96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAGO BORGES DE SANT ANA </t>
+  </si>
+  <si>
+    <t>14,68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAN SANTOS RODRIGUES </t>
+  </si>
+  <si>
+    <t>16,50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICARO DE OLIVEIRA SANTOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IGOR DORIGON DA ROCHA </t>
+  </si>
+  <si>
+    <t>556,04</t>
+  </si>
+  <si>
+    <t>JAIRO DE OLIVEIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>523,57</t>
+  </si>
+  <si>
+    <t>479,93</t>
+  </si>
+  <si>
+    <t>138,73</t>
+  </si>
+  <si>
+    <t>229,08</t>
+  </si>
+  <si>
+    <t>88,52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JIAN JORGE FRANCO </t>
+  </si>
+  <si>
+    <t>291,58</t>
+  </si>
+  <si>
+    <t>247,93</t>
+  </si>
+  <si>
+    <t>255,34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JONATHAN HERCILIO PERIN GOMES DA SILVA </t>
+  </si>
+  <si>
+    <t>116,91</t>
+  </si>
+  <si>
+    <t>662,90</t>
+  </si>
+  <si>
+    <t>202,65</t>
+  </si>
+  <si>
+    <t>215,45</t>
+  </si>
+  <si>
+    <t>123,05</t>
+  </si>
+  <si>
+    <t>176,34</t>
+  </si>
+  <si>
+    <t>530,98</t>
+  </si>
+  <si>
+    <t>67,44</t>
+  </si>
+  <si>
+    <t>160,21</t>
+  </si>
+  <si>
+    <t>479,77</t>
+  </si>
+  <si>
+    <t>311,73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KLENILSON DOS SANTOS FERREIRA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LARISSA DE SOUZA DUARTE CARDOSO </t>
+  </si>
+  <si>
+    <t>266,41</t>
+  </si>
+  <si>
+    <t>LEANDRO DOS SANTOS ABREU</t>
+  </si>
+  <si>
+    <t>312,19</t>
+  </si>
+  <si>
+    <t>345,47</t>
+  </si>
+  <si>
+    <t>LEONARDO ALVES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>77,00</t>
+  </si>
+  <si>
+    <t>56,44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LINDOMAR TEIXEIRA DA SILVA </t>
+  </si>
+  <si>
+    <t>49,90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUANA NASCIMENTO BATISTA </t>
+  </si>
+  <si>
+    <t>296,52</t>
+  </si>
+  <si>
+    <t>5,62</t>
+  </si>
+  <si>
+    <t>LUCAS DE LIMA RIBEIRO</t>
+  </si>
+  <si>
+    <t>3,07</t>
+  </si>
+  <si>
+    <t>LUCAS DE SOUZA DINIZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCAS DO NASCIMENTO ARAUJO </t>
+  </si>
+  <si>
+    <t>186,98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCAS GUEDES DE CARVALHO </t>
+  </si>
+  <si>
+    <t>531,47</t>
+  </si>
+  <si>
+    <t>145,83</t>
+  </si>
+  <si>
+    <t>235,42</t>
+  </si>
+  <si>
+    <t>161,50</t>
+  </si>
+  <si>
+    <t>17,07</t>
+  </si>
+  <si>
+    <t>481,68</t>
+  </si>
+  <si>
+    <t>LUCIANO PEREIRA DE SOUZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS FERNANDO DA SILVA </t>
+  </si>
+  <si>
+    <t>70,95</t>
+  </si>
+  <si>
+    <t>LUIS VITOR FERREIRA</t>
+  </si>
+  <si>
+    <t>118,19</t>
+  </si>
+  <si>
+    <t>413,78</t>
+  </si>
+  <si>
+    <t>465,57</t>
+  </si>
+  <si>
+    <t>365,23</t>
+  </si>
+  <si>
+    <t>518,90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELO BISPO DA COSTA </t>
+  </si>
+  <si>
+    <t>239,73</t>
+  </si>
+  <si>
+    <t>135,12</t>
+  </si>
+  <si>
+    <t>165,16</t>
+  </si>
+  <si>
+    <t>183,71</t>
+  </si>
+  <si>
+    <t>70,00</t>
+  </si>
+  <si>
+    <t>40,91</t>
+  </si>
+  <si>
+    <t>225,54</t>
+  </si>
+  <si>
+    <t>2,69</t>
+  </si>
+  <si>
+    <t>154,44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARLON DE OLIVEIRA BORGES </t>
+  </si>
+  <si>
+    <t>422,11</t>
+  </si>
+  <si>
+    <t>449,52</t>
+  </si>
+  <si>
+    <t>MATHEUS DE JESUS DOS SANTOS</t>
+  </si>
+  <si>
+    <t>289,55</t>
+  </si>
+  <si>
+    <t>144,95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATHEUS HENRIQUE FERREIRA MACHADO </t>
+  </si>
+  <si>
+    <t>99,80</t>
+  </si>
+  <si>
+    <t>128,31</t>
+  </si>
+  <si>
+    <t>MESSIAS DA SILVA SARAIVA</t>
+  </si>
+  <si>
+    <t>105,00</t>
+  </si>
+  <si>
+    <t>159,82</t>
+  </si>
+  <si>
+    <t>OSVALDO RIBEIRO GUIMARAES</t>
+  </si>
+  <si>
+    <t>114,57</t>
+  </si>
+  <si>
+    <t>PATRICK DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>110,30</t>
+  </si>
+  <si>
+    <t>PAULO HENRIQUE SAMPAIO FERREIRA</t>
+  </si>
+  <si>
+    <t>297,20</t>
+  </si>
+  <si>
+    <t>PAULO RICARDO DIAS MANGIARINI</t>
+  </si>
+  <si>
+    <t>166,82</t>
+  </si>
+  <si>
+    <t>117,87</t>
+  </si>
+  <si>
+    <t>3,21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAEL FERREIRA MARTINS DA SILVA </t>
+  </si>
+  <si>
+    <t>530,92</t>
+  </si>
+  <si>
+    <t>341,26</t>
+  </si>
+  <si>
+    <t>397,00</t>
+  </si>
+  <si>
+    <t>467,10</t>
+  </si>
+  <si>
+    <t>RICARDO SABINO DE CASTRO</t>
+  </si>
+  <si>
+    <t>316,41</t>
+  </si>
+  <si>
+    <t>194,24</t>
+  </si>
+  <si>
+    <t>100,42</t>
+  </si>
+  <si>
+    <t>355,59</t>
+  </si>
+  <si>
+    <t>RONALDO ADRIANO DAMARATT</t>
+  </si>
+  <si>
+    <t>631,33</t>
+  </si>
+  <si>
+    <t>RUAN HENRIQUE CUNHA GUIMARÃES</t>
+  </si>
+  <si>
+    <t>543,87</t>
+  </si>
+  <si>
+    <t>214,67</t>
+  </si>
+  <si>
+    <t>335,16</t>
+  </si>
+  <si>
+    <t>130,64</t>
+  </si>
+  <si>
+    <t>57,48</t>
+  </si>
+  <si>
+    <t>644,40</t>
+  </si>
+  <si>
+    <t>61,64</t>
+  </si>
+  <si>
+    <t>VALMIR APARECIDO CASTELANI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VICTOR DA SILVA CHAGAS </t>
+  </si>
+  <si>
+    <t>78,95</t>
+  </si>
+  <si>
+    <t>VICTOR FREITAS DOS SANTOS</t>
+  </si>
+  <si>
+    <t>425,53</t>
+  </si>
+  <si>
+    <t>119,07</t>
+  </si>
+  <si>
+    <t>30,09</t>
+  </si>
+  <si>
+    <t>WELINGTON PEREIRA DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>311,99</t>
+  </si>
+  <si>
+    <t>400,35</t>
+  </si>
+  <si>
+    <t>127,56</t>
+  </si>
+  <si>
+    <t>WESLEY HENRIQUE DA SILVA PEREIRA</t>
+  </si>
+  <si>
+    <t>399,96</t>
+  </si>
+  <si>
+    <t>WILLIAM DIAS SERRANO SILVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WILLIAM SILVA </t>
   </si>
 </sst>
 </file>
@@ -5392,7 +6109,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3AE4913-4281-44EC-9895-A3BCDA934E02}">
-  <dimension ref="A1:E4680"/>
+  <dimension ref="A1:E5156"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -84958,7 +85675,8100 @@
         <v>46082</v>
       </c>
     </row>
+    <row r="4681" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4681">
+        <v>200295</v>
+      </c>
+      <c r="B4681" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C4681" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4681" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4681" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4682" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4682">
+        <v>90026</v>
+      </c>
+      <c r="B4682" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C4682" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4682" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4682" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4683" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4683">
+        <v>32274</v>
+      </c>
+      <c r="B4683" t="s">
+        <v>280</v>
+      </c>
+      <c r="C4683" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4683" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4683" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4684" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4684">
+        <v>90691</v>
+      </c>
+      <c r="B4684" t="s">
+        <v>448</v>
+      </c>
+      <c r="C4684" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4684" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4684" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4685" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4685">
+        <v>61160</v>
+      </c>
+      <c r="B4685" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C4685" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4685" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4685" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4686" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4686">
+        <v>420062</v>
+      </c>
+      <c r="B4686" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C4686" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4686" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4686" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4687" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4687">
+        <v>21535</v>
+      </c>
+      <c r="B4687" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C4687" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4687" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4687" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4688" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4688">
+        <v>21474</v>
+      </c>
+      <c r="B4688" t="s">
+        <v>912</v>
+      </c>
+      <c r="C4688" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4688" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4688" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4689" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4689">
+        <v>32101</v>
+      </c>
+      <c r="B4689" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4689" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4689" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4689" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4690" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4690">
+        <v>32525</v>
+      </c>
+      <c r="B4690" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C4690" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D4690" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4690" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4691" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4691">
+        <v>100332</v>
+      </c>
+      <c r="B4691" t="s">
+        <v>857</v>
+      </c>
+      <c r="C4691" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D4691" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4691" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4692" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4692">
+        <v>420019</v>
+      </c>
+      <c r="B4692" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C4692" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D4692" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4692" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4693" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4693">
+        <v>200231</v>
+      </c>
+      <c r="B4693" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4693" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D4693" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4693" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4694" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4694">
+        <v>60663</v>
+      </c>
+      <c r="B4694" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4694" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4694" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4694" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4695" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4695">
+        <v>210113</v>
+      </c>
+      <c r="B4695" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C4695" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D4695" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4695" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4696" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4696">
+        <v>90078</v>
+      </c>
+      <c r="B4696" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C4696" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4696" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4696" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4697" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4697">
+        <v>100328</v>
+      </c>
+      <c r="B4697" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C4697" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4697" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4697" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4698" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4698">
+        <v>32134</v>
+      </c>
+      <c r="B4698" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4698" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D4698" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4698" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4699" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4699">
+        <v>61184</v>
+      </c>
+      <c r="B4699" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C4699" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4699" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4699" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4700" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4700">
+        <v>42002</v>
+      </c>
+      <c r="B4700" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C4700" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4700" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4700" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4701" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4701">
+        <v>138</v>
+      </c>
+      <c r="B4701" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4701" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D4701" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4701" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4702" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4702">
+        <v>32471</v>
+      </c>
+      <c r="B4702" t="s">
+        <v>859</v>
+      </c>
+      <c r="C4702" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D4702" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4702" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4703" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4703">
+        <v>41986</v>
+      </c>
+      <c r="B4703" t="s">
+        <v>860</v>
+      </c>
+      <c r="C4703" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D4703" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4703" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4704" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4704">
+        <v>90445</v>
+      </c>
+      <c r="B4704" t="s">
+        <v>350</v>
+      </c>
+      <c r="C4704" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4704" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4704" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4705" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4705">
+        <v>32223</v>
+      </c>
+      <c r="B4705" t="s">
+        <v>639</v>
+      </c>
+      <c r="C4705" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4705" t="s">
+        <v>1663</v>
+      </c>
+      <c r="E4705" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4706" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4706">
+        <v>90997</v>
+      </c>
+      <c r="B4706" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C4706" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4706" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4706" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4707" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4707">
+        <v>31969</v>
+      </c>
+      <c r="B4707" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4707" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D4707" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4707" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4708" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4708">
+        <v>21450</v>
+      </c>
+      <c r="B4708" t="s">
+        <v>642</v>
+      </c>
+      <c r="C4708" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4708" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4708" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4709" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4709">
+        <v>2647</v>
+      </c>
+      <c r="B4709" t="s">
+        <v>449</v>
+      </c>
+      <c r="C4709" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D4709" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4709" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4710" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4710">
+        <v>200475</v>
+      </c>
+      <c r="B4710" t="s">
+        <v>643</v>
+      </c>
+      <c r="C4710" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D4710" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4710" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4711" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4711">
+        <v>210107</v>
+      </c>
+      <c r="B4711" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C4711" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D4711" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4711" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4712" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4712">
+        <v>19349</v>
+      </c>
+      <c r="B4712" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C4712" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4712" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4712" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4713" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4713">
+        <v>200264</v>
+      </c>
+      <c r="B4713" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4713" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D4713" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4713" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4714" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4714">
+        <v>21392</v>
+      </c>
+      <c r="B4714" t="s">
+        <v>645</v>
+      </c>
+      <c r="C4714" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D4714" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4714" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4715" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4715">
+        <v>643</v>
+      </c>
+      <c r="B4715" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C4715" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4715" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4715" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4716" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4716">
+        <v>41974</v>
+      </c>
+      <c r="B4716" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C4716" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4716" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4716" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4717" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4717">
+        <v>61026</v>
+      </c>
+      <c r="B4717" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4717" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D4717" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4717" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4718" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4718">
+        <v>210052</v>
+      </c>
+      <c r="B4718" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C4718" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D4718" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4718" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4719" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4719">
+        <v>210114</v>
+      </c>
+      <c r="B4719" t="s">
+        <v>993</v>
+      </c>
+      <c r="C4719" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D4719" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4719" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4720" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4720">
+        <v>31781</v>
+      </c>
+      <c r="B4720" t="s">
+        <v>428</v>
+      </c>
+      <c r="C4720" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D4720" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4720" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4721" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4721">
+        <v>60698</v>
+      </c>
+      <c r="B4721" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4721" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4721" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4721" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4722" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4722">
+        <v>90911</v>
+      </c>
+      <c r="B4722" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C4722" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4722" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4722" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4723" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4723">
+        <v>420026</v>
+      </c>
+      <c r="B4723" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C4723" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D4723" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4723" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4724" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4724">
+        <v>2648</v>
+      </c>
+      <c r="B4724" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C4724" t="s">
+        <v>1671</v>
+      </c>
+      <c r="D4724" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4724" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4725" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4725">
+        <v>60898</v>
+      </c>
+      <c r="B4725" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4725" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4725" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4725" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4726" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4726">
+        <v>21393</v>
+      </c>
+      <c r="B4726" t="s">
+        <v>283</v>
+      </c>
+      <c r="C4726" t="s">
+        <v>1672</v>
+      </c>
+      <c r="D4726" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4726" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4727" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4727">
+        <v>200198</v>
+      </c>
+      <c r="B4727" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4727" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4727" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4727" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4728" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4728">
+        <v>32472</v>
+      </c>
+      <c r="B4728" t="s">
+        <v>918</v>
+      </c>
+      <c r="C4728" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D4728" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4728" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4729" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4729">
+        <v>32</v>
+      </c>
+      <c r="B4729" t="s">
+        <v>284</v>
+      </c>
+      <c r="C4729" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4729" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4729" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4730" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4730">
+        <v>21542</v>
+      </c>
+      <c r="B4730" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C4730" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D4730" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4730" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4731" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4731">
+        <v>200602</v>
+      </c>
+      <c r="B4731" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C4731" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4731" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4731" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4732" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4732">
+        <v>21517</v>
+      </c>
+      <c r="B4732" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C4732" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4732" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4732" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4733" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4733">
+        <v>2946</v>
+      </c>
+      <c r="B4733" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4733" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4733" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4733" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4734" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4734">
+        <v>99169</v>
+      </c>
+      <c r="B4734" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C4734" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4734" t="s">
+        <v>1676</v>
+      </c>
+      <c r="E4734" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4735" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4735">
+        <v>200333</v>
+      </c>
+      <c r="B4735" t="s">
+        <v>652</v>
+      </c>
+      <c r="C4735" t="s">
+        <v>1677</v>
+      </c>
+      <c r="D4735" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4735" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4736" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4736">
+        <v>31017</v>
+      </c>
+      <c r="B4736" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4736" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4736" t="s">
+        <v>1678</v>
+      </c>
+      <c r="E4736" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4737" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4737">
+        <v>19337</v>
+      </c>
+      <c r="B4737" t="s">
+        <v>995</v>
+      </c>
+      <c r="C4737" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4737" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4737" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4738" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4738">
+        <v>32523</v>
+      </c>
+      <c r="B4738" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C4738" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D4738" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4738" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4739" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4739">
+        <v>210056</v>
+      </c>
+      <c r="B4739" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C4739" t="s">
+        <v>1680</v>
+      </c>
+      <c r="D4739" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4739" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4740" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4740">
+        <v>32518</v>
+      </c>
+      <c r="B4740" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C4740" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D4740" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4740" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4741" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4741">
+        <v>19275</v>
+      </c>
+      <c r="B4741" t="s">
+        <v>519</v>
+      </c>
+      <c r="C4741" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4741" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4741" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4742" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4742">
+        <v>21588</v>
+      </c>
+      <c r="B4742" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C4742" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4742" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4742" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4743" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4743">
+        <v>210028</v>
+      </c>
+      <c r="B4743" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C4743" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D4743" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4743" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4744" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4744">
+        <v>210058</v>
+      </c>
+      <c r="B4744" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C4744" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D4744" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4744" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4745" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4745">
+        <v>19321</v>
+      </c>
+      <c r="B4745" t="s">
+        <v>863</v>
+      </c>
+      <c r="C4745" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4745" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4745" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4746" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4746">
+        <v>32090</v>
+      </c>
+      <c r="B4746" t="s">
+        <v>655</v>
+      </c>
+      <c r="C4746" t="s">
+        <v>1684</v>
+      </c>
+      <c r="D4746" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4746" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4747" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4747">
+        <v>220080</v>
+      </c>
+      <c r="B4747" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C4747" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D4747" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4747" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4748" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4748">
+        <v>32391</v>
+      </c>
+      <c r="B4748" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4748" t="s">
+        <v>1686</v>
+      </c>
+      <c r="D4748" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4748" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4749" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4749">
+        <v>42007</v>
+      </c>
+      <c r="B4749" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C4749" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4749" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4749" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4750" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4750">
+        <v>31446</v>
+      </c>
+      <c r="B4750" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4750" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D4750" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4750" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4751" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4751">
+        <v>32478</v>
+      </c>
+      <c r="B4751" t="s">
+        <v>997</v>
+      </c>
+      <c r="C4751" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D4751" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4751" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4752" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4752">
+        <v>32500</v>
+      </c>
+      <c r="B4752" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C4752" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4752" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4752" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4753" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4753">
+        <v>21589</v>
+      </c>
+      <c r="B4753" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C4753" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D4753" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4753" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4754" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4754">
+        <v>31995</v>
+      </c>
+      <c r="B4754" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C4754" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4754" t="s">
+        <v>1692</v>
+      </c>
+      <c r="E4754" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4755" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4755">
+        <v>220034</v>
+      </c>
+      <c r="B4755" t="s">
+        <v>657</v>
+      </c>
+      <c r="C4755" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D4755" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4755" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4756" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4756">
+        <v>31699</v>
+      </c>
+      <c r="B4756" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4756" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4756" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4756" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4757" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4757">
+        <v>19262</v>
+      </c>
+      <c r="B4757" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C4757" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D4757" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4757" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4758" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4758">
+        <v>200548</v>
+      </c>
+      <c r="B4758" t="s">
+        <v>999</v>
+      </c>
+      <c r="C4758" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4758" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4758" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4759" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4759">
+        <v>41471</v>
+      </c>
+      <c r="B4759" t="s">
+        <v>456</v>
+      </c>
+      <c r="C4759" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4759" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4759" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4760" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4760">
+        <v>200636</v>
+      </c>
+      <c r="B4760" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C4760" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4760" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4760" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4761" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4761">
+        <v>32529</v>
+      </c>
+      <c r="B4761" t="s">
+        <v>1470</v>
+      </c>
+      <c r="C4761" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D4761" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4761" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4762" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4762">
+        <v>60560</v>
+      </c>
+      <c r="B4762" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4762" t="s">
+        <v>1695</v>
+      </c>
+      <c r="D4762" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4762" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4763" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4763">
+        <v>19273</v>
+      </c>
+      <c r="B4763" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C4763" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4763" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4763" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4764" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4764">
+        <v>210053</v>
+      </c>
+      <c r="B4764" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C4764" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D4764" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4764" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4765" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4765">
+        <v>90790</v>
+      </c>
+      <c r="B4765" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4765" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4765" t="s">
+        <v>1698</v>
+      </c>
+      <c r="E4765" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4766" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4766">
+        <v>41462</v>
+      </c>
+      <c r="B4766" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C4766" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4766" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E4766" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4767" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4767">
+        <v>21537</v>
+      </c>
+      <c r="B4767" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C4767" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D4767" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4767" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4768" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4768">
+        <v>21211</v>
+      </c>
+      <c r="B4768" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4768" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4768" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4768" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4769" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4769">
+        <v>19282</v>
+      </c>
+      <c r="B4769" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C4769" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D4769" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4769" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4770" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4770">
+        <v>90402</v>
+      </c>
+      <c r="B4770" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C4770" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4770" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4770" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4771" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4771">
+        <v>31380</v>
+      </c>
+      <c r="B4771" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4771" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D4771" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4771" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4772" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4772">
+        <v>2502</v>
+      </c>
+      <c r="B4772" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4772" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4772" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4772" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4773" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4773">
+        <v>21498</v>
+      </c>
+      <c r="B4773" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C4773" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4773" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4773" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4774" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4774">
+        <v>200619</v>
+      </c>
+      <c r="B4774" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C4774" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D4774" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4774" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4775" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4775">
+        <v>21551</v>
+      </c>
+      <c r="B4775" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C4775" t="s">
+        <v>1704</v>
+      </c>
+      <c r="D4775" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4775" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4776" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4776">
+        <v>32492</v>
+      </c>
+      <c r="B4776" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C4776" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4776" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4776" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4777" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4777">
+        <v>220035</v>
+      </c>
+      <c r="B4777" t="s">
+        <v>525</v>
+      </c>
+      <c r="C4777" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D4777" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4777" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4778" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4778">
+        <v>32535</v>
+      </c>
+      <c r="B4778" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C4778" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D4778" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4778" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4779" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4779">
+        <v>61193</v>
+      </c>
+      <c r="B4779" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C4779" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4779" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4779" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4780" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4780">
+        <v>60460</v>
+      </c>
+      <c r="B4780" t="s">
+        <v>359</v>
+      </c>
+      <c r="C4780" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4780" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4780" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4781" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4781">
+        <v>61191</v>
+      </c>
+      <c r="B4781" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C4781" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4781" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4781" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4782" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4782">
+        <v>55</v>
+      </c>
+      <c r="B4782" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C4782" t="s">
+        <v>1708</v>
+      </c>
+      <c r="D4782" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4782" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4783" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4783">
+        <v>19347</v>
+      </c>
+      <c r="B4783" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C4783" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D4783" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4783" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4784" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4784">
+        <v>32430</v>
+      </c>
+      <c r="B4784" t="s">
+        <v>925</v>
+      </c>
+      <c r="C4784" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4784" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4784" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4785" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4785">
+        <v>21563</v>
+      </c>
+      <c r="B4785" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C4785" t="s">
+        <v>1710</v>
+      </c>
+      <c r="D4785" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4785" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4786" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4786">
+        <v>21388</v>
+      </c>
+      <c r="B4786" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C4786" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4786" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4786" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4787" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4787">
+        <v>2718</v>
+      </c>
+      <c r="B4787" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C4787" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D4787" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4787" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4788" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4788">
+        <v>420016</v>
+      </c>
+      <c r="B4788" t="s">
+        <v>927</v>
+      </c>
+      <c r="C4788" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D4788" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4788" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4789" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4789">
+        <v>200519</v>
+      </c>
+      <c r="B4789" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C4789" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D4789" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4789" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4790" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4790">
+        <v>200345</v>
+      </c>
+      <c r="B4790" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4790" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D4790" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4790" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4791" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4791">
+        <v>420075</v>
+      </c>
+      <c r="B4791" t="s">
+        <v>1715</v>
+      </c>
+      <c r="C4791" t="s">
+        <v>1716</v>
+      </c>
+      <c r="D4791" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4791" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4792" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4792">
+        <v>32344</v>
+      </c>
+      <c r="B4792" t="s">
+        <v>530</v>
+      </c>
+      <c r="C4792" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D4792" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4792" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4793" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4793">
+        <v>220037</v>
+      </c>
+      <c r="B4793" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4793" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D4793" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4793" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4794" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4794">
+        <v>220092</v>
+      </c>
+      <c r="B4794" t="s">
+        <v>667</v>
+      </c>
+      <c r="C4794" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D4794" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4794" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4795" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4795">
+        <v>32358</v>
+      </c>
+      <c r="B4795" t="s">
+        <v>198</v>
+      </c>
+      <c r="C4795" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4795" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4795" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4796" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4796">
+        <v>32487</v>
+      </c>
+      <c r="B4796" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C4796" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D4796" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4796" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4797" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4797">
+        <v>21573</v>
+      </c>
+      <c r="B4797" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C4797" t="s">
+        <v>1719</v>
+      </c>
+      <c r="D4797" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4797" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4798" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4798">
+        <v>200647</v>
+      </c>
+      <c r="B4798" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C4798" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D4798" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4798" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4799" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4799">
+        <v>2768</v>
+      </c>
+      <c r="B4799" t="s">
+        <v>459</v>
+      </c>
+      <c r="C4799" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D4799" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4799" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4800" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4800">
+        <v>31119</v>
+      </c>
+      <c r="B4800" t="s">
+        <v>291</v>
+      </c>
+      <c r="C4800" t="s">
+        <v>1723</v>
+      </c>
+      <c r="D4800" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4800" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4801" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4801">
+        <v>2616</v>
+      </c>
+      <c r="B4801" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4801" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4801" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4801" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4802" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4802">
+        <v>2911</v>
+      </c>
+      <c r="B4802" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4802" t="s">
+        <v>1724</v>
+      </c>
+      <c r="D4802" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4802" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4803" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4803">
+        <v>99167</v>
+      </c>
+      <c r="B4803" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C4803" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4803" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E4803" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4804" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4804">
+        <v>41780</v>
+      </c>
+      <c r="B4804" t="s">
+        <v>672</v>
+      </c>
+      <c r="C4804" t="s">
+        <v>1725</v>
+      </c>
+      <c r="D4804" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4804" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4805" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4805">
+        <v>31843</v>
+      </c>
+      <c r="B4805" t="s">
+        <v>539</v>
+      </c>
+      <c r="C4805" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4805" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4805" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4806" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4806">
+        <v>61186</v>
+      </c>
+      <c r="B4806" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C4806" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D4806" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4806" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4807" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4807">
+        <v>90787</v>
+      </c>
+      <c r="B4807" t="s">
+        <v>540</v>
+      </c>
+      <c r="C4807" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4807" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4807" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4808" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4808">
+        <v>90403</v>
+      </c>
+      <c r="B4808" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4808" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4808" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4808" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4809" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4809">
+        <v>2585</v>
+      </c>
+      <c r="B4809" t="s">
+        <v>293</v>
+      </c>
+      <c r="C4809" t="s">
+        <v>1726</v>
+      </c>
+      <c r="D4809" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4809" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4810" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4810">
+        <v>19298</v>
+      </c>
+      <c r="B4810" t="s">
+        <v>827</v>
+      </c>
+      <c r="C4810" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D4810" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4810" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4811" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4811">
+        <v>61046</v>
+      </c>
+      <c r="B4811" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4811" t="s">
+        <v>1728</v>
+      </c>
+      <c r="D4811" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4811" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4812" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4812">
+        <v>200616</v>
+      </c>
+      <c r="B4812" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C4812" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4812" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4812" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4813" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4813">
+        <v>99148</v>
+      </c>
+      <c r="B4813" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C4813" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4813" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E4813" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4814" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4814">
+        <v>32292</v>
+      </c>
+      <c r="B4814" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4814" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4814" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4814" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4815" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4815">
+        <v>2976</v>
+      </c>
+      <c r="B4815" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4815" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4815" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4815" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4816" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4816">
+        <v>32309</v>
+      </c>
+      <c r="B4816" t="s">
+        <v>294</v>
+      </c>
+      <c r="C4816" t="s">
+        <v>1731</v>
+      </c>
+      <c r="D4816" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4816" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4817" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4817">
+        <v>200630</v>
+      </c>
+      <c r="B4817" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C4817" t="s">
+        <v>1733</v>
+      </c>
+      <c r="D4817" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4817" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4818" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4818">
+        <v>2086</v>
+      </c>
+      <c r="B4818" t="s">
+        <v>296</v>
+      </c>
+      <c r="C4818" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4818" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4818" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4819" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4819">
+        <v>32519</v>
+      </c>
+      <c r="B4819" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C4819" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D4819" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4819" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4820" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4820">
+        <v>32314</v>
+      </c>
+      <c r="B4820" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4820" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D4820" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4820" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4821" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4821">
+        <v>21059</v>
+      </c>
+      <c r="B4821" t="s">
+        <v>206</v>
+      </c>
+      <c r="C4821" t="s">
+        <v>1734</v>
+      </c>
+      <c r="D4821" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4821" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4822" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4822">
+        <v>220033</v>
+      </c>
+      <c r="B4822" t="s">
+        <v>541</v>
+      </c>
+      <c r="C4822" t="s">
+        <v>1735</v>
+      </c>
+      <c r="D4822" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4822" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4823" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4823">
+        <v>90172</v>
+      </c>
+      <c r="B4823" t="s">
+        <v>1736</v>
+      </c>
+      <c r="C4823" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4823" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E4823" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4824" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4824">
+        <v>234</v>
+      </c>
+      <c r="B4824" t="s">
+        <v>207</v>
+      </c>
+      <c r="C4824" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D4824" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4824" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4825" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4825">
+        <v>21121</v>
+      </c>
+      <c r="B4825" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4825" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D4825" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4825" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4826" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4826">
+        <v>200648</v>
+      </c>
+      <c r="B4826" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C4826" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D4826" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4826" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4827" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4827">
+        <v>19310</v>
+      </c>
+      <c r="B4827" t="s">
+        <v>828</v>
+      </c>
+      <c r="C4827" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D4827" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4827" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4828" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4828">
+        <v>31672</v>
+      </c>
+      <c r="B4828" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4828" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D4828" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4828" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4829" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4829">
+        <v>32465</v>
+      </c>
+      <c r="B4829" t="s">
+        <v>681</v>
+      </c>
+      <c r="C4829" t="s">
+        <v>1740</v>
+      </c>
+      <c r="D4829" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4829" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4830" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4830">
+        <v>90988</v>
+      </c>
+      <c r="B4830" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C4830" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4830" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4830" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4831" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4831">
+        <v>19304</v>
+      </c>
+      <c r="B4831" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C4831" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4831" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4831" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4832" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4832">
+        <v>2293</v>
+      </c>
+      <c r="B4832" t="s">
+        <v>463</v>
+      </c>
+      <c r="C4832" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D4832" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4832" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4833" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4833">
+        <v>32438</v>
+      </c>
+      <c r="B4833" t="s">
+        <v>464</v>
+      </c>
+      <c r="C4833" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D4833" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4833" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4834" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4834">
+        <v>21004</v>
+      </c>
+      <c r="B4834" t="s">
+        <v>298</v>
+      </c>
+      <c r="C4834" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4834" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4834" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4835" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4835">
+        <v>99155</v>
+      </c>
+      <c r="B4835" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C4835" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4835" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E4835" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4836" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4836">
+        <v>32297</v>
+      </c>
+      <c r="B4836" t="s">
+        <v>300</v>
+      </c>
+      <c r="C4836" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4836" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4836" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4837" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4837">
+        <v>220062</v>
+      </c>
+      <c r="B4837" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C4837" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4837" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4837" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4838" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4838">
+        <v>21511</v>
+      </c>
+      <c r="B4838" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C4838" t="s">
+        <v>1743</v>
+      </c>
+      <c r="D4838" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4838" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4839" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4839">
+        <v>200514</v>
+      </c>
+      <c r="B4839" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C4839" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D4839" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4839" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4840" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4840">
+        <v>32217</v>
+      </c>
+      <c r="B4840" t="s">
+        <v>212</v>
+      </c>
+      <c r="C4840" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D4840" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4840" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4841" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4841">
+        <v>41803</v>
+      </c>
+      <c r="B4841" t="s">
+        <v>683</v>
+      </c>
+      <c r="C4841" t="s">
+        <v>1725</v>
+      </c>
+      <c r="D4841" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4841" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4842" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4842">
+        <v>200496</v>
+      </c>
+      <c r="B4842" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C4842" t="s">
+        <v>1744</v>
+      </c>
+      <c r="D4842" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4842" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4843" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4843">
+        <v>32522</v>
+      </c>
+      <c r="B4843" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C4843" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D4843" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4843" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4844" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4844">
+        <v>100209</v>
+      </c>
+      <c r="B4844" t="s">
+        <v>368</v>
+      </c>
+      <c r="C4844" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4844" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4844" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4845" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4845">
+        <v>210054</v>
+      </c>
+      <c r="B4845" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C4845" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D4845" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4845" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4846" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4846">
+        <v>909117</v>
+      </c>
+      <c r="B4846" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C4846" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4846" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4846" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4847" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4847">
+        <v>200139</v>
+      </c>
+      <c r="B4847" t="s">
+        <v>686</v>
+      </c>
+      <c r="C4847" t="s">
+        <v>1677</v>
+      </c>
+      <c r="D4847" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4847" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4848" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4848">
+        <v>32441</v>
+      </c>
+      <c r="B4848" t="s">
+        <v>872</v>
+      </c>
+      <c r="C4848" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4848" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4848" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4849" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4849">
+        <v>19125</v>
+      </c>
+      <c r="B4849" t="s">
+        <v>301</v>
+      </c>
+      <c r="C4849" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4849" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4849" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4850" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4850">
+        <v>21060</v>
+      </c>
+      <c r="B4850" t="s">
+        <v>930</v>
+      </c>
+      <c r="C4850" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D4850" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4850" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4851" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4851">
+        <v>200240</v>
+      </c>
+      <c r="B4851" t="s">
+        <v>931</v>
+      </c>
+      <c r="C4851" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4851" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4851" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4852" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4852">
+        <v>220038</v>
+      </c>
+      <c r="B4852" t="s">
+        <v>550</v>
+      </c>
+      <c r="C4852" t="s">
+        <v>1749</v>
+      </c>
+      <c r="D4852" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4852" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4853" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4853">
+        <v>41438</v>
+      </c>
+      <c r="B4853" t="s">
+        <v>216</v>
+      </c>
+      <c r="C4853" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4853" t="s">
+        <v>1750</v>
+      </c>
+      <c r="E4853" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4854" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4854">
+        <v>21437</v>
+      </c>
+      <c r="B4854" t="s">
+        <v>688</v>
+      </c>
+      <c r="C4854" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D4854" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4854" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4855" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4855">
+        <v>200617</v>
+      </c>
+      <c r="B4855" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C4855" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D4855" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4855" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4856" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4856">
+        <v>21221</v>
+      </c>
+      <c r="B4856" t="s">
+        <v>466</v>
+      </c>
+      <c r="C4856" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D4856" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4856" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4857" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4857">
+        <v>200075</v>
+      </c>
+      <c r="B4857" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4857" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D4857" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4857" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4858" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4858">
+        <v>61196</v>
+      </c>
+      <c r="B4858" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C4858" t="s">
+        <v>1752</v>
+      </c>
+      <c r="D4858" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4858" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4859" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4859">
+        <v>31776</v>
+      </c>
+      <c r="B4859" t="s">
+        <v>554</v>
+      </c>
+      <c r="C4859" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4859" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4859" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4860" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4860">
+        <v>909106</v>
+      </c>
+      <c r="B4860" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C4860" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4860" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4860" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4861" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4861">
+        <v>210115</v>
+      </c>
+      <c r="B4861" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C4861" t="s">
+        <v>1753</v>
+      </c>
+      <c r="D4861" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4861" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4862" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4862">
+        <v>41851</v>
+      </c>
+      <c r="B4862" t="s">
+        <v>689</v>
+      </c>
+      <c r="C4862" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D4862" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4862" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4863" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4863">
+        <v>21083</v>
+      </c>
+      <c r="B4863" t="s">
+        <v>690</v>
+      </c>
+      <c r="C4863" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D4863" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4863" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4864" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4864">
+        <v>60721</v>
+      </c>
+      <c r="B4864" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4864" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D4864" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4864" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4865" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4865">
+        <v>99119</v>
+      </c>
+      <c r="B4865" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C4865" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4865" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4865" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4866" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4866">
+        <v>200626</v>
+      </c>
+      <c r="B4866" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C4866" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D4866" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4866" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4867" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4867">
+        <v>420018</v>
+      </c>
+      <c r="B4867" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C4867" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D4867" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4867" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4868" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4868">
+        <v>909118</v>
+      </c>
+      <c r="B4868" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C4868" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4868" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4868" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4869" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4869">
+        <v>90980</v>
+      </c>
+      <c r="B4869" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C4869" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4869" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4869" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4870" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4870">
+        <v>420059</v>
+      </c>
+      <c r="B4870" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C4870" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D4870" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4870" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4871" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4871">
+        <v>21363</v>
+      </c>
+      <c r="B4871" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C4871" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4871" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4871" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4872" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4872">
+        <v>2692</v>
+      </c>
+      <c r="B4872" t="s">
+        <v>470</v>
+      </c>
+      <c r="C4872" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D4872" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4872" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4873" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4873">
+        <v>220076</v>
+      </c>
+      <c r="B4873" t="s">
+        <v>693</v>
+      </c>
+      <c r="C4873" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4873" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E4873" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4874" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4874">
+        <v>21102</v>
+      </c>
+      <c r="B4874" t="s">
+        <v>222</v>
+      </c>
+      <c r="C4874" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4874" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4874" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4875" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4875">
+        <v>200110</v>
+      </c>
+      <c r="B4875" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4875" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D4875" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4875" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4876" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4876">
+        <v>200361</v>
+      </c>
+      <c r="B4876" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4876" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4876" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4876" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4877" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4877">
+        <v>32229</v>
+      </c>
+      <c r="B4877" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4877" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4877" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4877" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4878" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4878">
+        <v>21499</v>
+      </c>
+      <c r="B4878" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C4878" t="s">
+        <v>1758</v>
+      </c>
+      <c r="D4878" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4878" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4879" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4879">
+        <v>100167</v>
+      </c>
+      <c r="B4879" t="s">
+        <v>304</v>
+      </c>
+      <c r="C4879" t="s">
+        <v>1695</v>
+      </c>
+      <c r="D4879" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4879" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4880" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4880">
+        <v>41579</v>
+      </c>
+      <c r="B4880" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4880" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4880" t="s">
+        <v>1521</v>
+      </c>
+      <c r="E4880" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4881" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4881">
+        <v>230043</v>
+      </c>
+      <c r="B4881" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C4881" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4881" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4881" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4882" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4882">
+        <v>210116</v>
+      </c>
+      <c r="B4882" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C4882" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4882" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E4882" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4883" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4883">
+        <v>60827</v>
+      </c>
+      <c r="B4883" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4883" t="s">
+        <v>1761</v>
+      </c>
+      <c r="D4883" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4883" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4884" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4884">
+        <v>32488</v>
+      </c>
+      <c r="B4884" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C4884" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D4884" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4884" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4885" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4885">
+        <v>200328</v>
+      </c>
+      <c r="B4885" t="s">
+        <v>374</v>
+      </c>
+      <c r="C4885" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D4885" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4885" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4886" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4886">
+        <v>31122</v>
+      </c>
+      <c r="B4886" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4886" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D4886" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4886" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4887" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4887">
+        <v>210117</v>
+      </c>
+      <c r="B4887" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C4887" t="s">
+        <v>1765</v>
+      </c>
+      <c r="D4887" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4887" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4888" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4888">
+        <v>21601</v>
+      </c>
+      <c r="B4888" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C4888" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D4888" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4888" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4889" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4889">
+        <v>200552</v>
+      </c>
+      <c r="B4889" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C4889" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4889" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4889" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4890" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4890">
+        <v>32369</v>
+      </c>
+      <c r="B4890" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4890" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4890" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4890" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4891" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4891">
+        <v>100283</v>
+      </c>
+      <c r="B4891" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C4891" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D4891" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4891" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4892" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4892">
+        <v>32361</v>
+      </c>
+      <c r="B4892" t="s">
+        <v>227</v>
+      </c>
+      <c r="C4892" t="s">
+        <v>1527</v>
+      </c>
+      <c r="D4892" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4892" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4893" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4893">
+        <v>32230</v>
+      </c>
+      <c r="B4893" t="s">
+        <v>228</v>
+      </c>
+      <c r="C4893" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D4893" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4893" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4894" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4894">
+        <v>99173</v>
+      </c>
+      <c r="B4894" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C4894" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4894" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4894" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4895" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4895">
+        <v>32043</v>
+      </c>
+      <c r="B4895" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4895" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4895" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4895" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4896" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4896">
+        <v>200086</v>
+      </c>
+      <c r="B4896" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C4896" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4896" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4896" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4897" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4897">
+        <v>31974</v>
+      </c>
+      <c r="B4897" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4897" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D4897" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4897" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4898" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4898">
+        <v>2493</v>
+      </c>
+      <c r="B4898" t="s">
+        <v>941</v>
+      </c>
+      <c r="C4898" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D4898" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4898" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4899" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4899">
+        <v>32360</v>
+      </c>
+      <c r="B4899" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4899" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D4899" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4899" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4900" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4900">
+        <v>200622</v>
+      </c>
+      <c r="B4900" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C4900" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D4900" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4900" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4901" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4901">
+        <v>21552</v>
+      </c>
+      <c r="B4901" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C4901" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D4901" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4901" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4902" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4902">
+        <v>32482</v>
+      </c>
+      <c r="B4902" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C4902" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4902" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4902" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4903" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4903">
+        <v>90845</v>
+      </c>
+      <c r="B4903" t="s">
+        <v>556</v>
+      </c>
+      <c r="C4903" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4903" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E4903" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4904" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4904">
+        <v>200004</v>
+      </c>
+      <c r="B4904" t="s">
+        <v>699</v>
+      </c>
+      <c r="C4904" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4904" t="s">
+        <v>1772</v>
+      </c>
+      <c r="E4904" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4905" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4905">
+        <v>32160</v>
+      </c>
+      <c r="B4905" t="s">
+        <v>700</v>
+      </c>
+      <c r="C4905" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D4905" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4905" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4906" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4906">
+        <v>90992</v>
+      </c>
+      <c r="B4906" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C4906" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4906" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4906" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4907" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4907">
+        <v>200177</v>
+      </c>
+      <c r="B4907" t="s">
+        <v>310</v>
+      </c>
+      <c r="C4907" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D4907" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4907" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4908" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4908">
+        <v>90182</v>
+      </c>
+      <c r="B4908" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C4908" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4908" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4908" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4909" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4909">
+        <v>1853</v>
+      </c>
+      <c r="B4909" t="s">
+        <v>945</v>
+      </c>
+      <c r="C4909" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4909" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4909" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4910" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4910">
+        <v>31814</v>
+      </c>
+      <c r="B4910" t="s">
+        <v>379</v>
+      </c>
+      <c r="C4910" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D4910" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4910" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4911" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4911">
+        <v>32508</v>
+      </c>
+      <c r="B4911" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C4911" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D4911" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4911" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4912" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4912">
+        <v>32280</v>
+      </c>
+      <c r="B4912" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4912" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4912" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4912" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4913" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4913">
+        <v>21603</v>
+      </c>
+      <c r="B4913" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C4913" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D4913" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4913" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4914" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4914">
+        <v>200577</v>
+      </c>
+      <c r="B4914" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C4914" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4914" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4914" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4915" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4915">
+        <v>19204</v>
+      </c>
+      <c r="B4915" t="s">
+        <v>557</v>
+      </c>
+      <c r="C4915" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4915" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4915" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4916" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4916">
+        <v>200372</v>
+      </c>
+      <c r="B4916" t="s">
+        <v>701</v>
+      </c>
+      <c r="C4916" t="s">
+        <v>1677</v>
+      </c>
+      <c r="D4916" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4916" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4917" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4917">
+        <v>41664</v>
+      </c>
+      <c r="B4917" t="s">
+        <v>946</v>
+      </c>
+      <c r="C4917" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4917" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4917" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4918" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4918">
+        <v>61170</v>
+      </c>
+      <c r="B4918" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C4918" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D4918" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4918" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4919" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4919">
+        <v>19340</v>
+      </c>
+      <c r="B4919" t="s">
+        <v>947</v>
+      </c>
+      <c r="C4919" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D4919" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4919" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4920" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4920">
+        <v>100274</v>
+      </c>
+      <c r="B4920" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C4920" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4920" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4920" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4921" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4921">
+        <v>90264</v>
+      </c>
+      <c r="B4921" t="s">
+        <v>381</v>
+      </c>
+      <c r="C4921" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4921" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4921" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4922" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4922">
+        <v>61187</v>
+      </c>
+      <c r="B4922" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C4922" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4922" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4922" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4923" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4923">
+        <v>61126</v>
+      </c>
+      <c r="B4923" t="s">
+        <v>311</v>
+      </c>
+      <c r="C4923" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4923" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4923" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4924" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4924">
+        <v>19246</v>
+      </c>
+      <c r="B4924" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C4924" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4924" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4924" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4925" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4925">
+        <v>21544</v>
+      </c>
+      <c r="B4925" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C4925" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D4925" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4925" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4926" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4926">
+        <v>21030</v>
+      </c>
+      <c r="B4926" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4926" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4926" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4926" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4927" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4927">
+        <v>41679</v>
+      </c>
+      <c r="B4927" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4927" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4927" t="s">
+        <v>1779</v>
+      </c>
+      <c r="E4927" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4928" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4928">
+        <v>90616</v>
+      </c>
+      <c r="B4928" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C4928" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4928" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E4928" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4929" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4929">
+        <v>200640</v>
+      </c>
+      <c r="B4929" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C4929" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D4929" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4929" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4930" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4930">
+        <v>61200</v>
+      </c>
+      <c r="B4930" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C4930" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D4930" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4930" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4931" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4931">
+        <v>32469</v>
+      </c>
+      <c r="B4931" t="s">
+        <v>881</v>
+      </c>
+      <c r="C4931" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4931" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E4931" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4932" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4932">
+        <v>99134</v>
+      </c>
+      <c r="B4932" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C4932" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4932" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4932" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4933" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4933">
+        <v>90442</v>
+      </c>
+      <c r="B4933" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C4933" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4933" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4933" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4934" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4934">
+        <v>200067</v>
+      </c>
+      <c r="B4934" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C4934" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4934" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4934" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4935" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4935">
+        <v>1210</v>
+      </c>
+      <c r="B4935" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4935" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4935" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4935" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4936" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4936">
+        <v>2255</v>
+      </c>
+      <c r="B4936" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C4936" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D4936" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4936" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4937" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4937">
+        <v>200550</v>
+      </c>
+      <c r="B4937" t="s">
+        <v>951</v>
+      </c>
+      <c r="C4937" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D4937" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4937" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4938" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4938">
+        <v>200426</v>
+      </c>
+      <c r="B4938" t="s">
+        <v>479</v>
+      </c>
+      <c r="C4938" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D4938" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4938" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4939" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4939">
+        <v>41849</v>
+      </c>
+      <c r="B4939" t="s">
+        <v>314</v>
+      </c>
+      <c r="C4939" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4939" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4939" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4940" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4940">
+        <v>90846</v>
+      </c>
+      <c r="B4940" t="s">
+        <v>717</v>
+      </c>
+      <c r="C4940" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4940" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4940" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4941" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4941">
+        <v>90991</v>
+      </c>
+      <c r="B4941" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C4941" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4941" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4941" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4942" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4942">
+        <v>60344</v>
+      </c>
+      <c r="B4942" t="s">
+        <v>385</v>
+      </c>
+      <c r="C4942" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D4942" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4942" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4943" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4943">
+        <v>305</v>
+      </c>
+      <c r="B4943" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4943" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D4943" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4943" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4944" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4944">
+        <v>21553</v>
+      </c>
+      <c r="B4944" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C4944" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4944" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4944" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4945" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4945">
+        <v>200638</v>
+      </c>
+      <c r="B4945" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C4945" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D4945" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4945" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4946" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4946">
+        <v>200387</v>
+      </c>
+      <c r="B4946" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4946" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4946" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4946" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4947" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4947">
+        <v>31680</v>
+      </c>
+      <c r="B4947" t="s">
+        <v>719</v>
+      </c>
+      <c r="C4947" t="s">
+        <v>1788</v>
+      </c>
+      <c r="D4947" t="s">
+        <v>1789</v>
+      </c>
+      <c r="E4947" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4948" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4948">
+        <v>2864</v>
+      </c>
+      <c r="B4948" t="s">
+        <v>236</v>
+      </c>
+      <c r="C4948" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4948" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4948" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4949" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4949">
+        <v>21239</v>
+      </c>
+      <c r="B4949" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C4949" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4949" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4949" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4950" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4950">
+        <v>60658</v>
+      </c>
+      <c r="B4950" t="s">
+        <v>481</v>
+      </c>
+      <c r="C4950" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4950" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4950" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4951" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4951">
+        <v>90318</v>
+      </c>
+      <c r="B4951" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C4951" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4951" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4951" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4952" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4952">
+        <v>200601</v>
+      </c>
+      <c r="B4952" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C4952" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4952" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4952" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4953" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4953">
+        <v>32367</v>
+      </c>
+      <c r="B4953" t="s">
+        <v>239</v>
+      </c>
+      <c r="C4953" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D4953" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4953" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4954" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4954">
+        <v>32481</v>
+      </c>
+      <c r="B4954" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C4954" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4954" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4954" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4955" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4955">
+        <v>21184</v>
+      </c>
+      <c r="B4955" t="s">
+        <v>882</v>
+      </c>
+      <c r="C4955" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D4955" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4955" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4956" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4956">
+        <v>21063</v>
+      </c>
+      <c r="B4956" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4956" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4956" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4956" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4957" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4957">
+        <v>32383</v>
+      </c>
+      <c r="B4957" t="s">
+        <v>723</v>
+      </c>
+      <c r="C4957" t="s">
+        <v>1791</v>
+      </c>
+      <c r="D4957" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4957" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4958" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4958">
+        <v>220021</v>
+      </c>
+      <c r="B4958" t="s">
+        <v>568</v>
+      </c>
+      <c r="C4958" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D4958" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4958" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4959" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4959">
+        <v>19315</v>
+      </c>
+      <c r="B4959" t="s">
+        <v>883</v>
+      </c>
+      <c r="C4959" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4959" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4959" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4960" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4960">
+        <v>200545</v>
+      </c>
+      <c r="B4960" t="s">
+        <v>884</v>
+      </c>
+      <c r="C4960" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D4960" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4960" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4961" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4961">
+        <v>200499</v>
+      </c>
+      <c r="B4961" t="s">
+        <v>885</v>
+      </c>
+      <c r="C4961" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D4961" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4961" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4962" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4962">
+        <v>99151</v>
+      </c>
+      <c r="B4962" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C4962" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4962" t="s">
+        <v>1676</v>
+      </c>
+      <c r="E4962" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4963" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4963">
+        <v>31726</v>
+      </c>
+      <c r="B4963" t="s">
+        <v>240</v>
+      </c>
+      <c r="C4963" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4963" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4963" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4964" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4964">
+        <v>230031</v>
+      </c>
+      <c r="B4964" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C4964" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4964" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4964" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4965" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4965">
+        <v>32485</v>
+      </c>
+      <c r="B4965" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C4965" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4965" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4965" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4966" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4966">
+        <v>42010</v>
+      </c>
+      <c r="B4966" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C4966" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4966" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4966" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4967" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4967">
+        <v>19235</v>
+      </c>
+      <c r="B4967" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C4967" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4967" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4967" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4968" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4968">
+        <v>19316</v>
+      </c>
+      <c r="B4968" t="s">
+        <v>887</v>
+      </c>
+      <c r="C4968" t="s">
+        <v>1795</v>
+      </c>
+      <c r="D4968" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4968" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4969" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4969">
+        <v>32384</v>
+      </c>
+      <c r="B4969" t="s">
+        <v>242</v>
+      </c>
+      <c r="C4969" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D4969" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4969" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4970" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4970">
+        <v>32450</v>
+      </c>
+      <c r="B4970" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C4970" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4970" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4970" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4971" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4971">
+        <v>31727</v>
+      </c>
+      <c r="B4971" t="s">
+        <v>243</v>
+      </c>
+      <c r="C4971" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D4971" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4971" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4972" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4972">
+        <v>200377</v>
+      </c>
+      <c r="B4972" t="s">
+        <v>729</v>
+      </c>
+      <c r="C4972" t="s">
+        <v>1677</v>
+      </c>
+      <c r="D4972" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4972" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4973" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4973">
+        <v>200506</v>
+      </c>
+      <c r="B4973" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C4973" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D4973" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4973" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4974" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4974">
+        <v>420079</v>
+      </c>
+      <c r="B4974" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C4974" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D4974" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4974" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4975" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4975">
+        <v>60969</v>
+      </c>
+      <c r="B4975" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4975" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D4975" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4975" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4976" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4976">
+        <v>32349</v>
+      </c>
+      <c r="B4976" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4976" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D4976" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4976" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4977" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4977">
+        <v>200199</v>
+      </c>
+      <c r="B4977" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4977" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D4977" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4977" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4978" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4978">
+        <v>200536</v>
+      </c>
+      <c r="B4978" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C4978" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4978" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4978" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4979" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4979">
+        <v>21546</v>
+      </c>
+      <c r="B4979" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C4979" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D4979" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4979" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4980" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4980">
+        <v>90093</v>
+      </c>
+      <c r="B4980" t="s">
+        <v>483</v>
+      </c>
+      <c r="C4980" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4980" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E4980" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4981" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4981">
+        <v>99186</v>
+      </c>
+      <c r="B4981" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C4981" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4981" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E4981" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4982" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4982">
+        <v>21453</v>
+      </c>
+      <c r="B4982" t="s">
+        <v>396</v>
+      </c>
+      <c r="C4982" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D4982" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4982" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4983" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4983">
+        <v>220039</v>
+      </c>
+      <c r="B4983" t="s">
+        <v>957</v>
+      </c>
+      <c r="C4983" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D4983" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4983" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4984" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4984">
+        <v>210047</v>
+      </c>
+      <c r="B4984" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C4984" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D4984" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4984" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4985" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4985">
+        <v>90931</v>
+      </c>
+      <c r="B4985" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C4985" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4985" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E4985" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4986" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4986">
+        <v>21368</v>
+      </c>
+      <c r="B4986" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C4986" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D4986" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4986" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4987" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4987">
+        <v>32446</v>
+      </c>
+      <c r="B4987" t="s">
+        <v>573</v>
+      </c>
+      <c r="C4987" t="s">
+        <v>1573</v>
+      </c>
+      <c r="D4987" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4987" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4988" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4988">
+        <v>200507</v>
+      </c>
+      <c r="B4988" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C4988" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4988" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4988" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4989" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4989">
+        <v>210032</v>
+      </c>
+      <c r="B4989" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C4989" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D4989" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4989" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4990" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4990">
+        <v>99121</v>
+      </c>
+      <c r="B4990" t="s">
+        <v>574</v>
+      </c>
+      <c r="C4990" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4990" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E4990" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4991" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4991">
+        <v>19004</v>
+      </c>
+      <c r="B4991" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C4991" t="s">
+        <v>1813</v>
+      </c>
+      <c r="D4991" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4991" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4992" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4992">
+        <v>100226</v>
+      </c>
+      <c r="B4992" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C4992" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D4992" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4992" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4993" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4993">
+        <v>200020</v>
+      </c>
+      <c r="B4993" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4993" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D4993" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4993" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4994" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4994">
+        <v>200633</v>
+      </c>
+      <c r="B4994" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C4994" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D4994" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4994" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4995" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4995">
+        <v>99157</v>
+      </c>
+      <c r="B4995" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C4995" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4995" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E4995" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4996" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4996">
+        <v>60745</v>
+      </c>
+      <c r="B4996" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4996" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4996" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4996" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4997" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4997">
+        <v>21584</v>
+      </c>
+      <c r="B4997" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C4997" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4997" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4997" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4998" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4998">
+        <v>19279</v>
+      </c>
+      <c r="B4998" t="s">
+        <v>575</v>
+      </c>
+      <c r="C4998" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D4998" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4998" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="4999" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4999">
+        <v>22022</v>
+      </c>
+      <c r="B4999" t="s">
+        <v>576</v>
+      </c>
+      <c r="C4999" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D4999" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E4999" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5000" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5000">
+        <v>21576</v>
+      </c>
+      <c r="B5000" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C5000" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D5000" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5000" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5001" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5001">
+        <v>220040</v>
+      </c>
+      <c r="B5001" t="s">
+        <v>1819</v>
+      </c>
+      <c r="C5001" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D5001" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5001" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5002" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5002">
+        <v>61065</v>
+      </c>
+      <c r="B5002" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5002" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5002" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5002" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5003" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5003">
+        <v>210061</v>
+      </c>
+      <c r="B5003" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C5003" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D5003" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5003" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5004" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5004">
+        <v>21618</v>
+      </c>
+      <c r="B5004" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C5004" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D5004" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5004" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5005" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5005">
+        <v>41997</v>
+      </c>
+      <c r="B5005" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C5005" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5005" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5005" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5006" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5006">
+        <v>32526</v>
+      </c>
+      <c r="B5006" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C5006" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D5006" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5006" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5007" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5007">
+        <v>32509</v>
+      </c>
+      <c r="B5007" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C5007" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D5007" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5007" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5008" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5008">
+        <v>32505</v>
+      </c>
+      <c r="B5008" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C5008" t="s">
+        <v>1587</v>
+      </c>
+      <c r="D5008" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5008" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5009" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5009">
+        <v>220013</v>
+      </c>
+      <c r="B5009" t="s">
+        <v>845</v>
+      </c>
+      <c r="C5009" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D5009" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5009" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5010" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5010">
+        <v>90708</v>
+      </c>
+      <c r="B5010" t="s">
+        <v>399</v>
+      </c>
+      <c r="C5010" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5010" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5010" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5011" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5011">
+        <v>210048</v>
+      </c>
+      <c r="B5011" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C5011" t="s">
+        <v>1826</v>
+      </c>
+      <c r="D5011" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5011" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5012" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5012">
+        <v>90856</v>
+      </c>
+      <c r="B5012" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C5012" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5012" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5012" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5013" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5013">
+        <v>200124</v>
+      </c>
+      <c r="B5013" t="s">
+        <v>752</v>
+      </c>
+      <c r="C5013" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5013" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E5013" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5014" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5014">
+        <v>19118</v>
+      </c>
+      <c r="B5014" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C5014" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5014" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5014" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5015" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5015">
+        <v>90427</v>
+      </c>
+      <c r="B5015" t="s">
+        <v>323</v>
+      </c>
+      <c r="C5015" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5015" t="s">
+        <v>1391</v>
+      </c>
+      <c r="E5015" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5016" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5016">
+        <v>2482</v>
+      </c>
+      <c r="B5016" t="s">
+        <v>324</v>
+      </c>
+      <c r="C5016" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5016" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5016" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5017" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5017">
+        <v>19300</v>
+      </c>
+      <c r="B5017" t="s">
+        <v>846</v>
+      </c>
+      <c r="C5017" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D5017" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5017" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5018" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5018">
+        <v>200278</v>
+      </c>
+      <c r="B5018" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C5018" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D5018" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5018" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5019" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5019">
+        <v>61188</v>
+      </c>
+      <c r="B5019" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C5019" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5019" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5019" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5020" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5020">
+        <v>60973</v>
+      </c>
+      <c r="B5020" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5020" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D5020" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5020" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5021" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5021">
+        <v>32466</v>
+      </c>
+      <c r="B5021" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C5021" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5021" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5021" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5022" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5022">
+        <v>220041</v>
+      </c>
+      <c r="B5022" t="s">
+        <v>893</v>
+      </c>
+      <c r="C5022" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D5022" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5022" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5023" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5023">
+        <v>41560</v>
+      </c>
+      <c r="B5023" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5023" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D5023" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5023" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5024" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5024">
+        <v>90226</v>
+      </c>
+      <c r="B5024" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5024" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5024" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5024" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5025" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5025">
+        <v>200191</v>
+      </c>
+      <c r="B5025" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C5025" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5025" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E5025" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5026" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5026">
+        <v>60811</v>
+      </c>
+      <c r="B5026" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5026" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5026" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5026" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5027" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5027">
+        <v>200574</v>
+      </c>
+      <c r="B5027" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C5027" t="s">
+        <v>1832</v>
+      </c>
+      <c r="D5027" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5027" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5028" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5028">
+        <v>2850</v>
+      </c>
+      <c r="B5028" t="s">
+        <v>962</v>
+      </c>
+      <c r="C5028" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5028" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5028" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5029" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5029">
+        <v>61097</v>
+      </c>
+      <c r="B5029" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5029" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D5029" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5029" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5030" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5030">
+        <v>32220</v>
+      </c>
+      <c r="B5030" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5030" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D5030" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5030" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5031" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5031">
+        <v>200535</v>
+      </c>
+      <c r="B5031" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C5031" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5031" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5031" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5032" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5032">
+        <v>200152</v>
+      </c>
+      <c r="B5032" t="s">
+        <v>403</v>
+      </c>
+      <c r="C5032" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D5032" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5032" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5033" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5033">
+        <v>200580</v>
+      </c>
+      <c r="B5033" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C5033" t="s">
+        <v>1835</v>
+      </c>
+      <c r="D5033" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5033" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5034" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5034">
+        <v>31683</v>
+      </c>
+      <c r="B5034" t="s">
+        <v>489</v>
+      </c>
+      <c r="C5034" t="s">
+        <v>1836</v>
+      </c>
+      <c r="D5034" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5034" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5035" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5035">
+        <v>32398</v>
+      </c>
+      <c r="B5035" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5035" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D5035" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5035" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5036" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5036">
+        <v>32530</v>
+      </c>
+      <c r="B5036" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C5036" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D5036" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5036" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5037" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5037">
+        <v>21227</v>
+      </c>
+      <c r="B5037" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C5037" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D5037" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5037" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5038" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5038">
+        <v>220001</v>
+      </c>
+      <c r="B5038" t="s">
+        <v>964</v>
+      </c>
+      <c r="C5038" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5038" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5038" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5039" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5039">
+        <v>2701</v>
+      </c>
+      <c r="B5039" t="s">
+        <v>585</v>
+      </c>
+      <c r="C5039" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D5039" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5039" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5040" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5040">
+        <v>99170</v>
+      </c>
+      <c r="B5040" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C5040" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5040" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E5040" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5041" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5041">
+        <v>32356</v>
+      </c>
+      <c r="B5041" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5041" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D5041" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5041" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5042" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5042">
+        <v>210049</v>
+      </c>
+      <c r="B5042" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C5042" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D5042" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5042" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5043" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5043">
+        <v>21568</v>
+      </c>
+      <c r="B5043" t="s">
+        <v>1841</v>
+      </c>
+      <c r="C5043" t="s">
+        <v>1842</v>
+      </c>
+      <c r="D5043" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5043" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5044" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5044">
+        <v>200430</v>
+      </c>
+      <c r="B5044" t="s">
+        <v>440</v>
+      </c>
+      <c r="C5044" t="s">
+        <v>1604</v>
+      </c>
+      <c r="D5044" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5044" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5045" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5045">
+        <v>21529</v>
+      </c>
+      <c r="B5045" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C5045" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D5045" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5045" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5046" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5046">
+        <v>99190</v>
+      </c>
+      <c r="B5046" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C5046" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5046" t="s">
+        <v>1845</v>
+      </c>
+      <c r="E5046" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5047" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5047">
+        <v>19278</v>
+      </c>
+      <c r="B5047" t="s">
+        <v>587</v>
+      </c>
+      <c r="C5047" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D5047" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5047" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5048" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5048">
+        <v>200378</v>
+      </c>
+      <c r="B5048" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5048" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D5048" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5048" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5049" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5049">
+        <v>21356</v>
+      </c>
+      <c r="B5049" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C5049" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5049" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5049" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5050" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5050">
+        <v>90201</v>
+      </c>
+      <c r="B5050" t="s">
+        <v>257</v>
+      </c>
+      <c r="C5050" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5050" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E5050" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5051" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5051">
+        <v>2936</v>
+      </c>
+      <c r="B5051" t="s">
+        <v>329</v>
+      </c>
+      <c r="C5051" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5051" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5051" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5052" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5052">
+        <v>61181</v>
+      </c>
+      <c r="B5052" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C5052" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5052" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5052" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5053" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5053">
+        <v>396</v>
+      </c>
+      <c r="B5053" t="s">
+        <v>258</v>
+      </c>
+      <c r="C5053" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D5053" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5053" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5054" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5054">
+        <v>21620</v>
+      </c>
+      <c r="B5054" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C5054" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5054" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5054" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5055" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5055">
+        <v>99142</v>
+      </c>
+      <c r="B5055" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C5055" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5055" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E5055" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5056" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5056">
+        <v>21525</v>
+      </c>
+      <c r="B5056" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C5056" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5056" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5056" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5057" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5057">
+        <v>19210</v>
+      </c>
+      <c r="B5057" t="s">
+        <v>493</v>
+      </c>
+      <c r="C5057" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D5057" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5057" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5058" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5058">
+        <v>19022</v>
+      </c>
+      <c r="B5058" t="s">
+        <v>594</v>
+      </c>
+      <c r="C5058" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5058" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5058" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5059" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5059">
+        <v>90430</v>
+      </c>
+      <c r="B5059" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C5059" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5059" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5059" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5060" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5060">
+        <v>61194</v>
+      </c>
+      <c r="B5060" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C5060" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D5060" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5060" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5061" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5061">
+        <v>90516</v>
+      </c>
+      <c r="B5061" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C5061" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5061" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E5061" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5062" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5062">
+        <v>32426</v>
+      </c>
+      <c r="B5062" t="s">
+        <v>771</v>
+      </c>
+      <c r="C5062" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5062" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5062" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5063" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5063">
+        <v>32490</v>
+      </c>
+      <c r="B5063" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C5063" t="s">
+        <v>1851</v>
+      </c>
+      <c r="D5063" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5063" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5064" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5064">
+        <v>91001</v>
+      </c>
+      <c r="B5064" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C5064" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5064" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5064" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5065" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5065">
+        <v>90825</v>
+      </c>
+      <c r="B5065" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C5065" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5065" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5065" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5066" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5066">
+        <v>60987</v>
+      </c>
+      <c r="B5066" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5066" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5066" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5066" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5067" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5067">
+        <v>32429</v>
+      </c>
+      <c r="B5067" t="s">
+        <v>408</v>
+      </c>
+      <c r="C5067" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D5067" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5067" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5068" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5068">
+        <v>32461</v>
+      </c>
+      <c r="B5068" t="s">
+        <v>597</v>
+      </c>
+      <c r="C5068" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5068" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5068" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5069" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5069">
+        <v>21599</v>
+      </c>
+      <c r="B5069" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C5069" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D5069" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5069" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5070" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5070">
+        <v>10150</v>
+      </c>
+      <c r="B5070" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C5070" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5070" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5070" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5071" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5071">
+        <v>220016</v>
+      </c>
+      <c r="B5071" t="s">
+        <v>775</v>
+      </c>
+      <c r="C5071" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D5071" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5071" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5072" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5072">
+        <v>200367</v>
+      </c>
+      <c r="B5072" t="s">
+        <v>261</v>
+      </c>
+      <c r="C5072" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D5072" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5072" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5073" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5073">
+        <v>210109</v>
+      </c>
+      <c r="B5073" t="s">
+        <v>968</v>
+      </c>
+      <c r="C5073" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D5073" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5073" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5074" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5074">
+        <v>114</v>
+      </c>
+      <c r="B5074" t="s">
+        <v>776</v>
+      </c>
+      <c r="C5074" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5074" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5074" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5075" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5075">
+        <v>32474</v>
+      </c>
+      <c r="B5075" t="s">
+        <v>970</v>
+      </c>
+      <c r="C5075" t="s">
+        <v>1859</v>
+      </c>
+      <c r="D5075" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5075" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5076" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5076">
+        <v>90905</v>
+      </c>
+      <c r="B5076" t="s">
+        <v>598</v>
+      </c>
+      <c r="C5076" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5076" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5076" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5077" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5077">
+        <v>21495</v>
+      </c>
+      <c r="B5077" t="s">
+        <v>850</v>
+      </c>
+      <c r="C5077" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5077" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5077" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5078" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5078">
+        <v>220017</v>
+      </c>
+      <c r="B5078" t="s">
+        <v>601</v>
+      </c>
+      <c r="C5078" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D5078" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5078" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5079" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5079">
+        <v>200651</v>
+      </c>
+      <c r="B5079" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C5079" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5079" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5079" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5080" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5080">
+        <v>99128</v>
+      </c>
+      <c r="B5080" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C5080" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5080" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E5080" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5081" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5081">
+        <v>19311</v>
+      </c>
+      <c r="B5081" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C5081" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5081" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5081" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5082" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5082">
+        <v>32176</v>
+      </c>
+      <c r="B5082" t="s">
+        <v>781</v>
+      </c>
+      <c r="C5082" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5082" t="s">
+        <v>1861</v>
+      </c>
+      <c r="E5082" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5083" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5083">
+        <v>21559</v>
+      </c>
+      <c r="B5083" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C5083" t="s">
+        <v>1862</v>
+      </c>
+      <c r="D5083" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5083" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5084" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5084">
+        <v>200306</v>
+      </c>
+      <c r="B5084" t="s">
+        <v>410</v>
+      </c>
+      <c r="C5084" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5084" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5084" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5085" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5085">
+        <v>200451</v>
+      </c>
+      <c r="B5085" t="s">
+        <v>499</v>
+      </c>
+      <c r="C5085" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D5085" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5085" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5086" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5086">
+        <v>90987</v>
+      </c>
+      <c r="B5086" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C5086" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5086" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5086" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5087" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5087">
+        <v>200094</v>
+      </c>
+      <c r="B5087" t="s">
+        <v>412</v>
+      </c>
+      <c r="C5087" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D5087" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5087" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5088" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5088">
+        <v>31487</v>
+      </c>
+      <c r="B5088" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5088" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D5088" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5088" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5089" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5089">
+        <v>2842</v>
+      </c>
+      <c r="B5089" t="s">
+        <v>263</v>
+      </c>
+      <c r="C5089" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D5089" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5089" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5090" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5090">
+        <v>31414</v>
+      </c>
+      <c r="B5090" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C5090" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5090" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5090" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5091" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5091">
+        <v>32521</v>
+      </c>
+      <c r="B5091" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C5091" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D5091" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5091" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5092" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5092">
+        <v>21153</v>
+      </c>
+      <c r="B5092" t="s">
+        <v>330</v>
+      </c>
+      <c r="C5092" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5092" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5092" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5093" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5093">
+        <v>420042</v>
+      </c>
+      <c r="B5093" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C5093" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D5093" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5093" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5094" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5094">
+        <v>2672</v>
+      </c>
+      <c r="B5094" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C5094" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5094" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5094" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5095" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5095">
+        <v>41955</v>
+      </c>
+      <c r="B5095" t="s">
+        <v>784</v>
+      </c>
+      <c r="C5095" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5095" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5095" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5096" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5096">
+        <v>200494</v>
+      </c>
+      <c r="B5096" t="s">
+        <v>973</v>
+      </c>
+      <c r="C5096" t="s">
+        <v>1866</v>
+      </c>
+      <c r="D5096" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5096" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5097" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5097">
+        <v>21490</v>
+      </c>
+      <c r="B5097" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C5097" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5097" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5097" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5098" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5098">
+        <v>200503</v>
+      </c>
+      <c r="B5098" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C5098" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D5098" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5098" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5099" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5099">
+        <v>200258</v>
+      </c>
+      <c r="B5099" t="s">
+        <v>501</v>
+      </c>
+      <c r="C5099" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D5099" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5099" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5100">
+        <v>200277</v>
+      </c>
+      <c r="B5100" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C5100" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5100" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5100" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5101">
+        <v>61089</v>
+      </c>
+      <c r="B5101" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5101" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5101" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5101" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5102">
+        <v>2204</v>
+      </c>
+      <c r="B5102" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C5102" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5102" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5102" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5103">
+        <v>220043</v>
+      </c>
+      <c r="B5103" t="s">
+        <v>788</v>
+      </c>
+      <c r="C5103" t="s">
+        <v>1868</v>
+      </c>
+      <c r="D5103" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5103" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5104">
+        <v>2559</v>
+      </c>
+      <c r="B5104" t="s">
+        <v>975</v>
+      </c>
+      <c r="C5104" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5104" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5104" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5105">
+        <v>220086</v>
+      </c>
+      <c r="B5105" t="s">
+        <v>789</v>
+      </c>
+      <c r="C5105" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D5105" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5105" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5106">
+        <v>19327</v>
+      </c>
+      <c r="B5106" t="s">
+        <v>1870</v>
+      </c>
+      <c r="C5106" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5106" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5106" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5107">
+        <v>32318</v>
+      </c>
+      <c r="B5107" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5107" t="s">
+        <v>1871</v>
+      </c>
+      <c r="D5107" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5107" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5108">
+        <v>909111</v>
+      </c>
+      <c r="B5108" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C5108" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5108" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5108" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5109">
+        <v>11197</v>
+      </c>
+      <c r="B5109" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C5109" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5109" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5109" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5110">
+        <v>32494</v>
+      </c>
+      <c r="B5110" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C5110" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5110" t="s">
+        <v>1873</v>
+      </c>
+      <c r="E5110" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5111">
+        <v>32395</v>
+      </c>
+      <c r="B5111" t="s">
+        <v>266</v>
+      </c>
+      <c r="C5111" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5111" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5111" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5112">
+        <v>99143</v>
+      </c>
+      <c r="B5112" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C5112" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5112" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E5112" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5113">
+        <v>21556</v>
+      </c>
+      <c r="B5113" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C5113" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D5113" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5113" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5114">
+        <v>90871</v>
+      </c>
+      <c r="B5114" t="s">
+        <v>794</v>
+      </c>
+      <c r="C5114" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5114" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E5114" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5115">
+        <v>2921</v>
+      </c>
+      <c r="B5115" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5115" t="s">
+        <v>1875</v>
+      </c>
+      <c r="D5115" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5115" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5116">
+        <v>90981</v>
+      </c>
+      <c r="B5116" t="s">
+        <v>977</v>
+      </c>
+      <c r="C5116" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5116" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E5116" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5117">
+        <v>909104</v>
+      </c>
+      <c r="B5117" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C5117" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5117" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5117" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5118">
+        <v>19095</v>
+      </c>
+      <c r="B5118" t="s">
+        <v>618</v>
+      </c>
+      <c r="C5118" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5118" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5118" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5119">
+        <v>200008</v>
+      </c>
+      <c r="B5119" t="s">
+        <v>338</v>
+      </c>
+      <c r="C5119" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D5119" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5119" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5120">
+        <v>41116</v>
+      </c>
+      <c r="B5120" t="s">
+        <v>339</v>
+      </c>
+      <c r="C5120" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D5120" t="s">
+        <v>1779</v>
+      </c>
+      <c r="E5120" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5121">
+        <v>41015</v>
+      </c>
+      <c r="B5121" t="s">
+        <v>795</v>
+      </c>
+      <c r="C5121" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5121" t="s">
+        <v>1878</v>
+      </c>
+      <c r="E5121" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5122">
+        <v>90850</v>
+      </c>
+      <c r="B5122" t="s">
+        <v>979</v>
+      </c>
+      <c r="C5122" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5122" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E5122" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5123">
+        <v>200125</v>
+      </c>
+      <c r="B5123" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5123" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5123" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5123" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5124">
+        <v>32520</v>
+      </c>
+      <c r="B5124" t="s">
+        <v>1640</v>
+      </c>
+      <c r="C5124" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D5124" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5124" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5125">
+        <v>99153</v>
+      </c>
+      <c r="B5125" t="s">
+        <v>1643</v>
+      </c>
+      <c r="C5125" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5125" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E5125" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5126">
+        <v>99160</v>
+      </c>
+      <c r="B5126" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C5126" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5126" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E5126" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5127">
+        <v>19320</v>
+      </c>
+      <c r="B5127" t="s">
+        <v>909</v>
+      </c>
+      <c r="C5127" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D5127" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5127" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5128">
+        <v>713</v>
+      </c>
+      <c r="B5128" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5128" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5128" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5128" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5129">
+        <v>41530</v>
+      </c>
+      <c r="B5129" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C5129" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5129" t="s">
+        <v>1750</v>
+      </c>
+      <c r="E5129" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5130">
+        <v>31693</v>
+      </c>
+      <c r="B5130" t="s">
+        <v>272</v>
+      </c>
+      <c r="C5130" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5130" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5130" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5131">
+        <v>19236</v>
+      </c>
+      <c r="B5131" t="s">
+        <v>1646</v>
+      </c>
+      <c r="C5131" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5131" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5131" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5132">
+        <v>21358</v>
+      </c>
+      <c r="B5132" t="s">
+        <v>445</v>
+      </c>
+      <c r="C5132" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5132" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5132" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5133">
+        <v>2752</v>
+      </c>
+      <c r="B5133" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C5133" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D5133" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5133" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5134">
+        <v>32516</v>
+      </c>
+      <c r="B5134" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C5134" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5134" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5134" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5135">
+        <v>61119</v>
+      </c>
+      <c r="B5135" t="s">
+        <v>274</v>
+      </c>
+      <c r="C5135" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5135" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5135" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5136">
+        <v>220048</v>
+      </c>
+      <c r="B5136" t="s">
+        <v>622</v>
+      </c>
+      <c r="C5136" t="s">
+        <v>1884</v>
+      </c>
+      <c r="D5136" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5136" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5137">
+        <v>90929</v>
+      </c>
+      <c r="B5137" t="s">
+        <v>807</v>
+      </c>
+      <c r="C5137" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5137" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E5137" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5138">
+        <v>19318</v>
+      </c>
+      <c r="B5138" t="s">
+        <v>1649</v>
+      </c>
+      <c r="C5138" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D5138" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5138" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5139">
+        <v>19329</v>
+      </c>
+      <c r="B5139" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C5139" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5139" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5139" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5140">
+        <v>32381</v>
+      </c>
+      <c r="B5140" t="s">
+        <v>623</v>
+      </c>
+      <c r="C5140" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5140" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5140" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5141">
+        <v>32462</v>
+      </c>
+      <c r="B5141" t="s">
+        <v>624</v>
+      </c>
+      <c r="C5141" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5141" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5141" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5142">
+        <v>32052</v>
+      </c>
+      <c r="B5142" t="s">
+        <v>275</v>
+      </c>
+      <c r="C5142" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5142" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5142" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5143">
+        <v>21515</v>
+      </c>
+      <c r="B5143" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C5143" t="s">
+        <v>1886</v>
+      </c>
+      <c r="D5143" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5143" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5144">
+        <v>21600</v>
+      </c>
+      <c r="B5144" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C5144" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D5144" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5144" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5145">
+        <v>61056</v>
+      </c>
+      <c r="B5145" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5145" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5145" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5145" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5146">
+        <v>61112</v>
+      </c>
+      <c r="B5146" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5146" t="s">
+        <v>1889</v>
+      </c>
+      <c r="D5146" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5146" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5147">
+        <v>200479</v>
+      </c>
+      <c r="B5147" t="s">
+        <v>812</v>
+      </c>
+      <c r="C5147" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5147" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5147" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5148">
+        <v>200344</v>
+      </c>
+      <c r="B5148" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5148" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D5148" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5148" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5149">
+        <v>200476</v>
+      </c>
+      <c r="B5149" t="s">
+        <v>814</v>
+      </c>
+      <c r="C5149" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D5149" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5149" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5150">
+        <v>19344</v>
+      </c>
+      <c r="B5150" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C5150" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5150" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5150" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5151">
+        <v>19249</v>
+      </c>
+      <c r="B5151" t="s">
+        <v>505</v>
+      </c>
+      <c r="C5151" t="s">
+        <v>1892</v>
+      </c>
+      <c r="D5151" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5151" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5152">
+        <v>21174</v>
+      </c>
+      <c r="B5152" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C5152" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5152" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5152" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5153">
+        <v>21491</v>
+      </c>
+      <c r="B5153" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C5153" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5153" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5153" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5154">
+        <v>41404</v>
+      </c>
+      <c r="B5154" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C5154" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5154" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5154" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5155">
+        <v>21595</v>
+      </c>
+      <c r="B5155" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C5155" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D5155" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5155" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5156">
+        <v>19257</v>
+      </c>
+      <c r="B5156" t="s">
+        <v>507</v>
+      </c>
+      <c r="C5156" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D5156" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5156" s="1">
+        <v>46113</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E4680" xr:uid="{D3AE4913-4281-44EC-9895-A3BCDA934E02}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
